--- a/diseases/d114/2026-2029.xlsx
+++ b/diseases/d114/2026-2029.xlsx
@@ -16365,16 +16365,16 @@
         </is>
       </c>
       <c r="N92" t="n">
-        <v>698</v>
+        <v>702</v>
       </c>
       <c r="O92" t="n">
-        <v>698</v>
+        <v>702</v>
       </c>
       <c r="Q92" t="n">
         <v>0</v>
       </c>
       <c r="R92" t="n">
-        <v>2.563622650024814</v>
+        <v>2.578313897302893</v>
       </c>
       <c r="S92" t="inlineStr">
         <is>
@@ -18293,16 +18293,16 @@
         </is>
       </c>
       <c r="N103" t="n">
-        <v>100</v>
+        <v>131</v>
       </c>
       <c r="O103" t="n">
-        <v>100</v>
+        <v>131</v>
       </c>
       <c r="Q103" t="n">
         <v>0</v>
       </c>
       <c r="R103" t="n">
-        <v>0.367281181951979</v>
+        <v>0.4811383483570925</v>
       </c>
       <c r="S103" t="inlineStr">
         <is>
@@ -19492,7 +19492,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>26858</v>
+        <v>26893</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d114/2026-2029.xlsx
+++ b/diseases/d114/2026-2029.xlsx
@@ -17853,16 +17853,16 @@
         </is>
       </c>
       <c r="N98" t="n">
-        <v>704</v>
+        <v>707</v>
       </c>
       <c r="O98" t="n">
-        <v>704</v>
+        <v>707</v>
       </c>
       <c r="Q98" t="n">
         <v>0</v>
       </c>
       <c r="R98" t="n">
-        <v>2.585659520941932</v>
+        <v>2.596677956400492</v>
       </c>
       <c r="S98" t="inlineStr">
         <is>
@@ -19781,16 +19781,16 @@
         </is>
       </c>
       <c r="N109" t="n">
-        <v>154</v>
+        <v>184</v>
       </c>
       <c r="O109" t="n">
-        <v>154</v>
+        <v>184</v>
       </c>
       <c r="Q109" t="n">
         <v>0</v>
       </c>
       <c r="R109" t="n">
-        <v>0.5656130202060476</v>
+        <v>0.6757973747916414</v>
       </c>
       <c r="S109" t="inlineStr">
         <is>
@@ -20980,7 +20980,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>26925</v>
+        <v>26958</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d114/2026-2029.xlsx
+++ b/diseases/d114/2026-2029.xlsx
@@ -913,9 +913,6 @@
       <c r="O3" t="n">
         <v>266</v>
       </c>
-      <c r="Q3" t="n">
-        <v>0</v>
-      </c>
       <c r="S3" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -1306,9 +1303,6 @@
       <c r="O5" t="n">
         <v>121</v>
       </c>
-      <c r="Q5" t="n">
-        <v>0</v>
-      </c>
       <c r="R5" t="n">
         <v>1.343280566460305</v>
       </c>
@@ -1454,9 +1448,6 @@
       <c r="O6" t="n">
         <v>63</v>
       </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
       <c r="R6" t="n">
         <v>1.120649777644407</v>
       </c>
@@ -1850,9 +1841,6 @@
       <c r="O8" t="n">
         <v>51</v>
       </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
       <c r="R8" t="n">
         <v>0.9021776711557081</v>
       </c>
@@ -2495,7 +2483,7 @@
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN11" t="b">
@@ -2642,9 +2630,6 @@
       <c r="O12" t="n">
         <v>102</v>
       </c>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
       <c r="R12" t="n">
         <v>0.9531778036849013</v>
       </c>
@@ -3926,9 +3911,6 @@
       <c r="O20" t="n">
         <v>202</v>
       </c>
-      <c r="Q20" t="n">
-        <v>0</v>
-      </c>
       <c r="S20" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -4319,9 +4301,6 @@
       <c r="O22" t="n">
         <v>89</v>
       </c>
-      <c r="Q22" t="n">
-        <v>0</v>
-      </c>
       <c r="R22" t="n">
         <v>0.9880328133468356</v>
       </c>
@@ -4467,9 +4446,6 @@
       <c r="O23" t="n">
         <v>51</v>
       </c>
-      <c r="Q23" t="n">
-        <v>0</v>
-      </c>
       <c r="R23" t="n">
         <v>0.9071926771407101</v>
       </c>
@@ -4863,9 +4839,6 @@
       <c r="O25" t="n">
         <v>48</v>
       </c>
-      <c r="Q25" t="n">
-        <v>0</v>
-      </c>
       <c r="R25" t="n">
         <v>0.8491083963818431</v>
       </c>
@@ -5508,7 +5481,7 @@
       </c>
       <c r="AM28" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN28" t="b">
@@ -5655,9 +5628,6 @@
       <c r="O29" t="n">
         <v>87</v>
       </c>
-      <c r="Q29" t="n">
-        <v>0</v>
-      </c>
       <c r="R29" t="n">
         <v>0.8130045972606511</v>
       </c>
@@ -6791,9 +6761,6 @@
       <c r="O36" t="n">
         <v>280</v>
       </c>
-      <c r="Q36" t="n">
-        <v>0</v>
-      </c>
       <c r="S36" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -7184,9 +7151,6 @@
       <c r="O38" t="n">
         <v>120</v>
       </c>
-      <c r="Q38" t="n">
-        <v>0</v>
-      </c>
       <c r="R38" t="n">
         <v>1.332179074175509</v>
       </c>
@@ -7332,9 +7296,6 @@
       <c r="O39" t="n">
         <v>58</v>
       </c>
-      <c r="Q39" t="n">
-        <v>0</v>
-      </c>
       <c r="R39" t="n">
         <v>1.0317093191012</v>
       </c>
@@ -7728,9 +7689,6 @@
       <c r="O41" t="n">
         <v>51</v>
       </c>
-      <c r="Q41" t="n">
-        <v>0</v>
-      </c>
       <c r="R41" t="n">
         <v>0.9021776711557081</v>
       </c>
@@ -8373,7 +8331,7 @@
       </c>
       <c r="AM44" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN44" t="b">
@@ -8520,9 +8478,6 @@
       <c r="O45" t="n">
         <v>96</v>
       </c>
-      <c r="Q45" t="n">
-        <v>0</v>
-      </c>
       <c r="R45" t="n">
         <v>0.8971085211152012</v>
       </c>
@@ -9508,9 +9463,6 @@
       <c r="O51" t="n">
         <v>1385</v>
       </c>
-      <c r="Q51" t="n">
-        <v>0</v>
-      </c>
       <c r="R51" t="n">
         <v>5.08684437003491</v>
       </c>
@@ -9656,9 +9608,6 @@
       <c r="O52" t="n">
         <v>229</v>
       </c>
-      <c r="Q52" t="n">
-        <v>0</v>
-      </c>
       <c r="S52" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -10049,9 +9998,6 @@
       <c r="O54" t="n">
         <v>141</v>
       </c>
-      <c r="Q54" t="n">
-        <v>0</v>
-      </c>
       <c r="R54" t="n">
         <v>1.565310412156223</v>
       </c>
@@ -10197,9 +10143,6 @@
       <c r="O55" t="n">
         <v>94</v>
       </c>
-      <c r="Q55" t="n">
-        <v>0</v>
-      </c>
       <c r="R55" t="n">
         <v>1.672080620612289</v>
       </c>
@@ -10593,9 +10536,6 @@
       <c r="O57" t="n">
         <v>47</v>
       </c>
-      <c r="Q57" t="n">
-        <v>0</v>
-      </c>
       <c r="R57" t="n">
         <v>0.8314186381238879</v>
       </c>
@@ -10989,9 +10929,6 @@
       <c r="O59" t="n">
         <v>97</v>
       </c>
-      <c r="Q59" t="n">
-        <v>0</v>
-      </c>
       <c r="R59" t="n">
         <v>1.834522652477674</v>
       </c>
@@ -11238,7 +11175,7 @@
       </c>
       <c r="AM60" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN60" t="b">
@@ -11385,9 +11322,6 @@
       <c r="O61" t="n">
         <v>80</v>
       </c>
-      <c r="Q61" t="n">
-        <v>0</v>
-      </c>
       <c r="R61" t="n">
         <v>0.7475904342626677</v>
       </c>
@@ -12373,9 +12307,6 @@
       <c r="O67" t="n">
         <v>1084</v>
       </c>
-      <c r="Q67" t="n">
-        <v>0</v>
-      </c>
       <c r="R67" t="n">
         <v>3.981328012359453</v>
       </c>
@@ -12521,9 +12452,6 @@
       <c r="O68" t="n">
         <v>157</v>
       </c>
-      <c r="Q68" t="n">
-        <v>0</v>
-      </c>
       <c r="S68" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -12914,9 +12842,6 @@
       <c r="O70" t="n">
         <v>126</v>
       </c>
-      <c r="Q70" t="n">
-        <v>0</v>
-      </c>
       <c r="R70" t="n">
         <v>1.398788027884284</v>
       </c>
@@ -13062,9 +12987,6 @@
       <c r="O71" t="n">
         <v>48</v>
       </c>
-      <c r="Q71" t="n">
-        <v>0</v>
-      </c>
       <c r="R71" t="n">
         <v>0.8538284020147859</v>
       </c>
@@ -13458,9 +13380,6 @@
       <c r="O73" t="n">
         <v>50</v>
       </c>
-      <c r="Q73" t="n">
-        <v>0</v>
-      </c>
       <c r="R73" t="n">
         <v>0.8844879128977531</v>
       </c>
@@ -13854,9 +13773,6 @@
       <c r="O75" t="n">
         <v>85</v>
       </c>
-      <c r="Q75" t="n">
-        <v>0</v>
-      </c>
       <c r="R75" t="n">
         <v>1.607571396501055</v>
       </c>
@@ -14103,7 +14019,7 @@
       </c>
       <c r="AM76" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN76" t="b">
@@ -14250,9 +14166,6 @@
       <c r="O77" t="n">
         <v>108</v>
       </c>
-      <c r="Q77" t="n">
-        <v>0</v>
-      </c>
       <c r="R77" t="n">
         <v>1.009247086254601</v>
       </c>
@@ -15238,9 +15151,6 @@
       <c r="O83" t="n">
         <v>367</v>
       </c>
-      <c r="Q83" t="n">
-        <v>0</v>
-      </c>
       <c r="R83" t="n">
         <v>0.1051468994726364</v>
       </c>
@@ -15386,9 +15296,6 @@
       <c r="O84" t="n">
         <v>764</v>
       </c>
-      <c r="Q84" t="n">
-        <v>0</v>
-      </c>
       <c r="R84" t="n">
         <v>2.80602823011312</v>
       </c>
@@ -15534,9 +15441,6 @@
       <c r="O85" t="n">
         <v>165</v>
       </c>
-      <c r="Q85" t="n">
-        <v>0</v>
-      </c>
       <c r="R85" t="n">
         <v>1.831746226991325</v>
       </c>
@@ -15682,9 +15586,6 @@
       <c r="O86" t="n">
         <v>52</v>
       </c>
-      <c r="Q86" t="n">
-        <v>0</v>
-      </c>
       <c r="R86" t="n">
         <v>0.9249807688493514</v>
       </c>
@@ -16078,9 +15979,6 @@
       <c r="O88" t="n">
         <v>53</v>
       </c>
-      <c r="Q88" t="n">
-        <v>0</v>
-      </c>
       <c r="R88" t="n">
         <v>0.9375571876716183</v>
       </c>
@@ -16474,9 +16372,6 @@
       <c r="O90" t="n">
         <v>72</v>
       </c>
-      <c r="Q90" t="n">
-        <v>0</v>
-      </c>
       <c r="R90" t="n">
         <v>1.361707535859717</v>
       </c>
@@ -16723,7 +16618,7 @@
       </c>
       <c r="AM91" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN91" t="b">
@@ -16865,16 +16760,13 @@
         </is>
       </c>
       <c r="N92" t="n">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="O92" t="n">
-        <v>113</v>
-      </c>
-      <c r="Q92" t="n">
-        <v>0</v>
+        <v>112</v>
       </c>
       <c r="R92" t="n">
-        <v>1.055971488396018</v>
+        <v>1.046626607967735</v>
       </c>
       <c r="S92" t="inlineStr">
         <is>
@@ -17027,10 +16919,10 @@
         </is>
       </c>
       <c r="N93" t="n">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="O93" t="n">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="U93" t="inlineStr">
         <is>
@@ -17266,9 +17158,6 @@
       <c r="O94" t="n">
         <v>633</v>
       </c>
-      <c r="Q94" t="n">
-        <v>0</v>
-      </c>
       <c r="R94" t="n">
         <v>0.1813569138043021</v>
       </c>
@@ -17414,9 +17303,6 @@
       <c r="O95" t="n">
         <v>611</v>
       </c>
-      <c r="Q95" t="n">
-        <v>0</v>
-      </c>
       <c r="R95" t="n">
         <v>0.1750538299122094</v>
       </c>
@@ -17562,9 +17448,6 @@
       <c r="O96" t="n">
         <v>626</v>
       </c>
-      <c r="Q96" t="n">
-        <v>0</v>
-      </c>
       <c r="R96" t="n">
         <v>0.1793513871113635</v>
       </c>
@@ -17710,9 +17593,6 @@
       <c r="O97" t="n">
         <v>651</v>
       </c>
-      <c r="Q97" t="n">
-        <v>0</v>
-      </c>
       <c r="R97" t="n">
         <v>0.186513982443287</v>
       </c>
@@ -17858,9 +17738,6 @@
       <c r="O98" t="n">
         <v>707</v>
       </c>
-      <c r="Q98" t="n">
-        <v>0</v>
-      </c>
       <c r="R98" t="n">
         <v>2.596677956400492</v>
       </c>
@@ -18006,9 +17883,6 @@
       <c r="O99" t="n">
         <v>68</v>
       </c>
-      <c r="Q99" t="n">
-        <v>0</v>
-      </c>
       <c r="R99" t="n">
         <v>1.209590236187614</v>
       </c>
@@ -18402,9 +18276,6 @@
       <c r="O101" t="n">
         <v>112</v>
       </c>
-      <c r="Q101" t="n">
-        <v>0</v>
-      </c>
       <c r="R101" t="n">
         <v>1.981252924890967</v>
       </c>
@@ -18793,16 +18664,13 @@
         </is>
       </c>
       <c r="N103" t="n">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="O103" t="n">
-        <v>143</v>
-      </c>
-      <c r="Q103" t="n">
-        <v>0</v>
+        <v>142</v>
       </c>
       <c r="R103" t="n">
-        <v>1.336317901244518</v>
+        <v>1.326973020816235</v>
       </c>
       <c r="S103" t="inlineStr">
         <is>
@@ -18955,10 +18823,10 @@
         </is>
       </c>
       <c r="N104" t="n">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="O104" t="n">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="U104" t="inlineStr">
         <is>
@@ -19194,9 +19062,6 @@
       <c r="O105" t="n">
         <v>671</v>
       </c>
-      <c r="Q105" t="n">
-        <v>0</v>
-      </c>
       <c r="R105" t="n">
         <v>0.1922440587088257</v>
       </c>
@@ -19342,9 +19207,6 @@
       <c r="O106" t="n">
         <v>839</v>
       </c>
-      <c r="Q106" t="n">
-        <v>0</v>
-      </c>
       <c r="R106" t="n">
         <v>0.2403766993393514</v>
       </c>
@@ -19490,9 +19352,6 @@
       <c r="O107" t="n">
         <v>1110</v>
       </c>
-      <c r="Q107" t="n">
-        <v>0</v>
-      </c>
       <c r="R107" t="n">
         <v>0.3180192327374018</v>
       </c>
@@ -19638,9 +19497,6 @@
       <c r="O108" t="n">
         <v>1115</v>
       </c>
-      <c r="Q108" t="n">
-        <v>0</v>
-      </c>
       <c r="R108" t="n">
         <v>0.3194517518037865</v>
       </c>
@@ -19786,9 +19642,6 @@
       <c r="O109" t="n">
         <v>184</v>
       </c>
-      <c r="Q109" t="n">
-        <v>0</v>
-      </c>
       <c r="R109" t="n">
         <v>0.6757973747916414</v>
       </c>
@@ -19929,16 +19782,13 @@
         </is>
       </c>
       <c r="N110" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="O110" t="n">
-        <v>6</v>
-      </c>
-      <c r="Q110" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="R110" t="n">
-        <v>0.1067285502518482</v>
+        <v>0.2134571005036965</v>
       </c>
       <c r="S110" t="inlineStr">
         <is>
@@ -20091,10 +19941,10 @@
         </is>
       </c>
       <c r="N111" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="O111" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="U111" t="inlineStr">
         <is>
@@ -20325,16 +20175,13 @@
         </is>
       </c>
       <c r="N112" t="n">
-        <v>11</v>
+        <v>44</v>
       </c>
       <c r="O112" t="n">
-        <v>11</v>
-      </c>
-      <c r="Q112" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="R112" t="n">
-        <v>0.1945873408375057</v>
+        <v>0.7783493633500227</v>
       </c>
       <c r="S112" t="inlineStr">
         <is>
@@ -20487,10 +20334,10 @@
         </is>
       </c>
       <c r="N113" t="n">
-        <v>11</v>
+        <v>44</v>
       </c>
       <c r="O113" t="n">
-        <v>11</v>
+        <v>44</v>
       </c>
       <c r="U113" t="inlineStr">
         <is>
@@ -20726,9 +20573,6 @@
       <c r="O114" t="n">
         <v>1166</v>
       </c>
-      <c r="Q114" t="n">
-        <v>0</v>
-      </c>
       <c r="R114" t="n">
         <v>0.3340634462809103</v>
       </c>
@@ -20797,6 +20641,151 @@
         </is>
       </c>
       <c r="BC114" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>D114</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>salmonellosis</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>Salmonellosis</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>D114</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>Salmonellosis</t>
+        </is>
+      </c>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>沙门氏菌病</t>
+        </is>
+      </c>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L115" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="M115" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N115" t="n">
+        <v>1060</v>
+      </c>
+      <c r="O115" t="n">
+        <v>1060</v>
+      </c>
+      <c r="R115" t="n">
+        <v>0.3036940420735548</v>
+      </c>
+      <c r="S115" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO115" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP115" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR115" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS115" t="inlineStr"/>
+      <c r="AT115" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU115" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV115" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW115" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX115" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY115" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ115" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA115" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB115" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC115" t="inlineStr">
         <is>
           <t>api; api</t>
         </is>
@@ -20835,7 +20824,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-08</t>
         </is>
       </c>
     </row>
@@ -20918,7 +20907,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="10">
@@ -20928,7 +20917,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="11">
@@ -20980,7 +20969,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>26958</v>
+        <v>28055</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d114/2026-2029.xlsx
+++ b/diseases/d114/2026-2029.xlsx
@@ -15436,13 +15436,13 @@
         </is>
       </c>
       <c r="N85" t="n">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="O85" t="n">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="R85" t="n">
-        <v>1.831746226991325</v>
+        <v>1.887253688415304</v>
       </c>
       <c r="S85" t="inlineStr">
         <is>
@@ -17839,12 +17839,12 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Switzerland</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -17878,95 +17878,81 @@
         </is>
       </c>
       <c r="N99" t="n">
-        <v>68</v>
+        <v>290</v>
       </c>
       <c r="O99" t="n">
-        <v>68</v>
+        <v>290</v>
       </c>
       <c r="R99" t="n">
-        <v>1.209590236187614</v>
+        <v>3.219432762590813</v>
       </c>
       <c r="S99" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U99" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1200</t>
-        </is>
-      </c>
-      <c r="AA99" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO99" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP99" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ99" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AS99" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1200</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR99" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS99" t="inlineStr"/>
       <c r="AT99" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU99" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV99" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>foph_idd</t>
         </is>
       </c>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Switzerland FOPH IDD</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>rest_api</t>
         </is>
       </c>
       <c r="AZ99" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>foph_idd</t>
         </is>
       </c>
       <c r="BA99" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Switzerland FOPH IDD</t>
         </is>
       </c>
       <c r="BB99" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
         </is>
       </c>
       <c r="BC99" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>rest_api</t>
         </is>
       </c>
     </row>
@@ -17993,7 +17979,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -18042,98 +18028,23 @@
       <c r="O100" t="n">
         <v>68</v>
       </c>
+      <c r="R100" t="n">
+        <v>1.209590236187614</v>
+      </c>
+      <c r="S100" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U100" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1200</t>
         </is>
       </c>
-      <c r="V100" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1200</t>
-        </is>
-      </c>
-      <c r="W100" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X100" t="inlineStr">
-        <is>
-          <t>Salmonella, other</t>
-        </is>
-      </c>
-      <c r="Y100" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z100" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA100" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB100" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC100" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD100" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE100" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF100" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG100" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH100" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI100" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ100" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK100" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; Residual Salmonella category excluding Typhi and Paratyphi; retain as its own non-additive series.</t>
-        </is>
-      </c>
-      <c r="AM100" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN100" t="b">
-        <v>1</v>
       </c>
       <c r="AO100" t="inlineStr">
         <is>
@@ -18227,17 +18138,17 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -18271,22 +18182,39 @@
         </is>
       </c>
       <c r="N101" t="n">
-        <v>112</v>
+        <v>68</v>
       </c>
       <c r="O101" t="n">
-        <v>112</v>
-      </c>
-      <c r="R101" t="n">
-        <v>1.981252924890967</v>
-      </c>
-      <c r="S101" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>68</v>
       </c>
       <c r="U101" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_302_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1200</t>
+        </is>
+      </c>
+      <c r="V101" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1200</t>
+        </is>
+      </c>
+      <c r="W101" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X101" t="inlineStr">
+        <is>
+          <t>Salmonella, other</t>
+        </is>
+      </c>
+      <c r="Y101" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z101" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -18294,6 +18222,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB101" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC101" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD101" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE101" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF101" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG101" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH101" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI101" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ101" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK101" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; Residual Salmonella category excluding Typhi and Paratyphi; retain as its own non-additive series.</t>
+        </is>
+      </c>
+      <c r="AM101" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN101" t="b">
+        <v>1</v>
+      </c>
       <c r="AO101" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -18306,12 +18292,12 @@
       </c>
       <c r="AQ101" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AS101" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_302_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1200</t>
         </is>
       </c>
       <c r="AT101" t="n">
@@ -18319,47 +18305,47 @@
       </c>
       <c r="AU101" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV101" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ101" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA101" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB101" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC101" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -18386,7 +18372,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -18435,98 +18421,23 @@
       <c r="O102" t="n">
         <v>112</v>
       </c>
+      <c r="R102" t="n">
+        <v>1.981252924890967</v>
+      </c>
+      <c r="S102" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U102" t="inlineStr">
         <is>
           <t>SER_NO_FHI_302_MONTHLY</t>
         </is>
       </c>
-      <c r="V102" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_302_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W102" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X102" t="inlineStr">
-        <is>
-          <t>Salmonellose</t>
-        </is>
-      </c>
-      <c r="Y102" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z102" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA102" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB102" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC102" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD102" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE102" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF102" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG102" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH102" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI102" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ102" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK102" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
-        </is>
-      </c>
-      <c r="AM102" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN102" t="b">
-        <v>1</v>
       </c>
       <c r="AO102" t="inlineStr">
         <is>
@@ -18620,17 +18531,17 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -18664,22 +18575,39 @@
         </is>
       </c>
       <c r="N103" t="n">
-        <v>142</v>
+        <v>112</v>
       </c>
       <c r="O103" t="n">
-        <v>142</v>
-      </c>
-      <c r="R103" t="n">
-        <v>1.326973020816235</v>
-      </c>
-      <c r="S103" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>112</v>
       </c>
       <c r="U103" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_SALMONELLA</t>
+          <t>SER_NO_FHI_302_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V103" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_302_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W103" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X103" t="inlineStr">
+        <is>
+          <t>Salmonellose</t>
+        </is>
+      </c>
+      <c r="Y103" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z103" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -18687,6 +18615,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB103" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC103" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD103" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE103" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF103" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG103" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH103" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI103" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ103" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK103" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM103" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN103" t="b">
+        <v>1</v>
+      </c>
       <c r="AO103" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -18704,7 +18690,7 @@
       </c>
       <c r="AS103" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_SALMONELLA</t>
+          <t>SER_NO_FHI_302_MONTHLY</t>
         </is>
       </c>
       <c r="AT103" t="n">
@@ -18717,42 +18703,42 @@
       </c>
       <c r="AV103" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ103" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA103" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB103" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC103" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -18779,7 +18765,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -18828,98 +18814,23 @@
       <c r="O104" t="n">
         <v>142</v>
       </c>
+      <c r="R104" t="n">
+        <v>1.326973020816235</v>
+      </c>
+      <c r="S104" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U104" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_SALMONELLA</t>
         </is>
       </c>
-      <c r="V104" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_SALMONELLA</t>
-        </is>
-      </c>
-      <c r="W104" t="inlineStr">
-        <is>
-          <t>SRC_SE_FOHM_SMINET</t>
-        </is>
-      </c>
-      <c r="X104" t="inlineStr">
-        <is>
-          <t>Salmonellainfektion</t>
-        </is>
-      </c>
-      <c r="Y104" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z104" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA104" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB104" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC104" t="inlineStr">
-        <is>
-          <t>country:SE:national</t>
-        </is>
-      </c>
-      <c r="AD104" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE104" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF104" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG104" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH104" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI104" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ104" t="inlineStr">
-        <is>
-          <t>SE_FOHM_SMINET_current</t>
-        </is>
-      </c>
-      <c r="AK104" t="inlineStr">
-        <is>
-          <t>Sweden FHM SmiNet national monthly notification series; Retain FHM source scope alongside separate Typhi and Paratyphi categories.</t>
-        </is>
-      </c>
-      <c r="AM104" t="inlineStr">
-        <is>
-          <t>revised</t>
-        </is>
-      </c>
-      <c r="AN104" t="b">
-        <v>1</v>
       </c>
       <c r="AO104" t="inlineStr">
         <is>
@@ -19013,17 +18924,17 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -19048,7 +18959,7 @@
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M105" t="inlineStr">
@@ -19057,81 +18968,170 @@
         </is>
       </c>
       <c r="N105" t="n">
-        <v>671</v>
+        <v>142</v>
       </c>
       <c r="O105" t="n">
-        <v>671</v>
-      </c>
-      <c r="R105" t="n">
-        <v>0.1922440587088257</v>
-      </c>
-      <c r="S105" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>142</v>
+      </c>
+      <c r="U105" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_SALMONELLA</t>
+        </is>
+      </c>
+      <c r="V105" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_SALMONELLA</t>
+        </is>
+      </c>
+      <c r="W105" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X105" t="inlineStr">
+        <is>
+          <t>Salmonellainfektion</t>
+        </is>
+      </c>
+      <c r="Y105" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z105" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA105" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB105" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC105" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD105" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE105" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF105" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG105" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH105" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI105" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ105" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK105" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; Retain FHM source scope alongside separate Typhi and Paratyphi categories.</t>
+        </is>
+      </c>
+      <c r="AM105" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN105" t="b">
+        <v>1</v>
       </c>
       <c r="AO105" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP105" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR105" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS105" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ105" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS105" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_SALMONELLA</t>
+        </is>
+      </c>
       <c r="AT105" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU105" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV105" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ105" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA105" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB105" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC105" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -19193,7 +19193,7 @@
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="M106" t="inlineStr">
@@ -19202,13 +19202,13 @@
         </is>
       </c>
       <c r="N106" t="n">
-        <v>839</v>
+        <v>671</v>
       </c>
       <c r="O106" t="n">
-        <v>839</v>
+        <v>671</v>
       </c>
       <c r="R106" t="n">
-        <v>0.2403766993393514</v>
+        <v>0.1922440587088257</v>
       </c>
       <c r="S106" t="inlineStr">
         <is>
@@ -19338,7 +19338,7 @@
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="M107" t="inlineStr">
@@ -19347,13 +19347,13 @@
         </is>
       </c>
       <c r="N107" t="n">
-        <v>1110</v>
+        <v>839</v>
       </c>
       <c r="O107" t="n">
-        <v>1110</v>
+        <v>839</v>
       </c>
       <c r="R107" t="n">
-        <v>0.3180192327374018</v>
+        <v>0.2403766993393514</v>
       </c>
       <c r="S107" t="inlineStr">
         <is>
@@ -19483,7 +19483,7 @@
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="M108" t="inlineStr">
@@ -19492,13 +19492,13 @@
         </is>
       </c>
       <c r="N108" t="n">
-        <v>1115</v>
+        <v>1110</v>
       </c>
       <c r="O108" t="n">
-        <v>1115</v>
+        <v>1110</v>
       </c>
       <c r="R108" t="n">
-        <v>0.3194517518037865</v>
+        <v>0.3180192327374018</v>
       </c>
       <c r="S108" t="inlineStr">
         <is>
@@ -19598,12 +19598,12 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -19628,22 +19628,22 @@
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="M109" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N109" t="n">
-        <v>184</v>
+        <v>1115</v>
       </c>
       <c r="O109" t="n">
-        <v>184</v>
+        <v>1115</v>
       </c>
       <c r="R109" t="n">
-        <v>0.6757973747916414</v>
+        <v>0.3194517518037865</v>
       </c>
       <c r="S109" t="inlineStr">
         <is>
@@ -19676,42 +19676,42 @@
       </c>
       <c r="AV109" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ109" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA109" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB109" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC109" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -19743,12 +19743,12 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -19782,95 +19782,81 @@
         </is>
       </c>
       <c r="N110" t="n">
-        <v>12</v>
+        <v>184</v>
       </c>
       <c r="O110" t="n">
-        <v>12</v>
+        <v>184</v>
       </c>
       <c r="R110" t="n">
-        <v>0.2134571005036965</v>
+        <v>0.6757973747916414</v>
       </c>
       <c r="S110" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U110" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1200</t>
-        </is>
-      </c>
-      <c r="AA110" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO110" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP110" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ110" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AS110" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1200</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR110" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS110" t="inlineStr"/>
       <c r="AT110" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU110" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV110" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ110" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA110" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB110" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC110" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -19897,7 +19883,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -19941,103 +19927,28 @@
         </is>
       </c>
       <c r="N111" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="O111" t="n">
-        <v>12</v>
+        <v>15</v>
+      </c>
+      <c r="R111" t="n">
+        <v>0.2668213756296206</v>
+      </c>
+      <c r="S111" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="U111" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1200</t>
         </is>
       </c>
-      <c r="V111" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1200</t>
-        </is>
-      </c>
-      <c r="W111" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X111" t="inlineStr">
-        <is>
-          <t>Salmonella, other</t>
-        </is>
-      </c>
-      <c r="Y111" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z111" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA111" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB111" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC111" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD111" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE111" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF111" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG111" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH111" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI111" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ111" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK111" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; Residual Salmonella category excluding Typhi and Paratyphi; retain as its own non-additive series.</t>
-        </is>
-      </c>
-      <c r="AM111" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN111" t="b">
-        <v>1</v>
       </c>
       <c r="AO111" t="inlineStr">
         <is>
@@ -20131,17 +20042,17 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -20175,22 +20086,39 @@
         </is>
       </c>
       <c r="N112" t="n">
-        <v>44</v>
+        <v>15</v>
       </c>
       <c r="O112" t="n">
-        <v>44</v>
-      </c>
-      <c r="R112" t="n">
-        <v>0.7783493633500227</v>
-      </c>
-      <c r="S112" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>15</v>
       </c>
       <c r="U112" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_302_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1200</t>
+        </is>
+      </c>
+      <c r="V112" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1200</t>
+        </is>
+      </c>
+      <c r="W112" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X112" t="inlineStr">
+        <is>
+          <t>Salmonella, other</t>
+        </is>
+      </c>
+      <c r="Y112" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z112" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
@@ -20198,6 +20126,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB112" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC112" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD112" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE112" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF112" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG112" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH112" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI112" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ112" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK112" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; Residual Salmonella category excluding Typhi and Paratyphi; retain as its own non-additive series.</t>
+        </is>
+      </c>
+      <c r="AM112" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN112" t="b">
+        <v>1</v>
+      </c>
       <c r="AO112" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -20210,12 +20196,12 @@
       </c>
       <c r="AQ112" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AS112" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_302_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1200</t>
         </is>
       </c>
       <c r="AT112" t="n">
@@ -20223,47 +20209,47 @@
       </c>
       <c r="AU112" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV112" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ112" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA112" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB112" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC112" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -20290,7 +20276,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -20339,98 +20325,23 @@
       <c r="O113" t="n">
         <v>44</v>
       </c>
+      <c r="R113" t="n">
+        <v>0.7783493633500227</v>
+      </c>
+      <c r="S113" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U113" t="inlineStr">
         <is>
           <t>SER_NO_FHI_302_MONTHLY</t>
         </is>
       </c>
-      <c r="V113" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_302_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W113" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X113" t="inlineStr">
-        <is>
-          <t>Salmonellose</t>
-        </is>
-      </c>
-      <c r="Y113" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z113" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA113" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB113" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC113" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD113" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE113" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF113" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG113" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH113" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI113" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ113" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK113" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
-        </is>
-      </c>
-      <c r="AM113" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN113" t="b">
-        <v>1</v>
       </c>
       <c r="AO113" t="inlineStr">
         <is>
@@ -20524,17 +20435,17 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -20568,81 +20479,170 @@
         </is>
       </c>
       <c r="N114" t="n">
-        <v>1166</v>
+        <v>44</v>
       </c>
       <c r="O114" t="n">
-        <v>1166</v>
-      </c>
-      <c r="R114" t="n">
-        <v>0.3340634462809103</v>
-      </c>
-      <c r="S114" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>44</v>
+      </c>
+      <c r="U114" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_302_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V114" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_302_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W114" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X114" t="inlineStr">
+        <is>
+          <t>Salmonellose</t>
+        </is>
+      </c>
+      <c r="Y114" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z114" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA114" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB114" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC114" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD114" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE114" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF114" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG114" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH114" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI114" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ114" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK114" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM114" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN114" t="b">
+        <v>1</v>
       </c>
       <c r="AO114" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP114" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR114" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS114" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ114" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS114" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_302_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT114" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU114" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV114" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ114" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA114" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB114" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC114" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -20704,7 +20704,7 @@
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M115" t="inlineStr">
@@ -20713,13 +20713,13 @@
         </is>
       </c>
       <c r="N115" t="n">
-        <v>1060</v>
+        <v>1166</v>
       </c>
       <c r="O115" t="n">
-        <v>1060</v>
+        <v>1166</v>
       </c>
       <c r="R115" t="n">
-        <v>0.3036940420735548</v>
+        <v>0.3340634462809103</v>
       </c>
       <c r="S115" t="inlineStr">
         <is>
@@ -20786,6 +20786,151 @@
         </is>
       </c>
       <c r="BC115" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>D114</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>salmonellosis</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>Salmonellosis</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>D114</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>Salmonellosis</t>
+        </is>
+      </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>沙门氏菌病</t>
+        </is>
+      </c>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L116" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="M116" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N116" t="n">
+        <v>1060</v>
+      </c>
+      <c r="O116" t="n">
+        <v>1060</v>
+      </c>
+      <c r="R116" t="n">
+        <v>0.3036940420735548</v>
+      </c>
+      <c r="S116" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO116" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP116" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR116" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS116" t="inlineStr"/>
+      <c r="AT116" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU116" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV116" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW116" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX116" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY116" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ116" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA116" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB116" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC116" t="inlineStr">
         <is>
           <t>api; api</t>
         </is>
@@ -20907,7 +21052,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="10">
@@ -20917,7 +21062,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="11">
@@ -20969,7 +21114,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>28055</v>
+        <v>28353</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d114/2026-2029.xlsx
+++ b/diseases/d114/2026-2029.xlsx
@@ -15291,13 +15291,13 @@
         </is>
       </c>
       <c r="N84" t="n">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="O84" t="n">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="R84" t="n">
-        <v>2.80602823011312</v>
+        <v>2.80970104193264</v>
       </c>
       <c r="S84" t="inlineStr">
         <is>
@@ -17733,13 +17733,13 @@
         </is>
       </c>
       <c r="N98" t="n">
-        <v>707</v>
+        <v>714</v>
       </c>
       <c r="O98" t="n">
-        <v>707</v>
+        <v>714</v>
       </c>
       <c r="R98" t="n">
-        <v>2.596677956400492</v>
+        <v>2.62238763913713</v>
       </c>
       <c r="S98" t="inlineStr">
         <is>
@@ -19782,13 +19782,13 @@
         </is>
       </c>
       <c r="N110" t="n">
-        <v>184</v>
+        <v>241</v>
       </c>
       <c r="O110" t="n">
-        <v>184</v>
+        <v>241</v>
       </c>
       <c r="R110" t="n">
-        <v>0.6757973747916414</v>
+        <v>0.8851476485042695</v>
       </c>
       <c r="S110" t="inlineStr">
         <is>
@@ -21114,7 +21114,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>28353</v>
+        <v>28418</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d114/2026-2029.xlsx
+++ b/diseases/d114/2026-2029.xlsx
@@ -3906,10 +3906,10 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="O20" t="n">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="S20" t="inlineStr">
         <is>
@@ -4062,10 +4062,10 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="O21" t="n">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="U21" t="inlineStr">
         <is>
@@ -9603,10 +9603,10 @@
         </is>
       </c>
       <c r="N52" t="n">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="O52" t="n">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="S52" t="inlineStr">
         <is>
@@ -9759,10 +9759,10 @@
         </is>
       </c>
       <c r="N53" t="n">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="O53" t="n">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="U53" t="inlineStr">
         <is>
@@ -12447,10 +12447,10 @@
         </is>
       </c>
       <c r="N68" t="n">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="O68" t="n">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="S68" t="inlineStr">
         <is>
@@ -12603,10 +12603,10 @@
         </is>
       </c>
       <c r="N69" t="n">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="O69" t="n">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="U69" t="inlineStr">
         <is>
@@ -15291,13 +15291,13 @@
         </is>
       </c>
       <c r="N84" t="n">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="O84" t="n">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="R84" t="n">
-        <v>2.80970104193264</v>
+        <v>2.813373853752159</v>
       </c>
       <c r="S84" t="inlineStr">
         <is>
@@ -15397,12 +15397,12 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>CH</t>
+          <t>CA-ON</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>Ontario, Canada</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -15436,81 +15436,92 @@
         </is>
       </c>
       <c r="N85" t="n">
-        <v>170</v>
+        <v>147</v>
       </c>
       <c r="O85" t="n">
-        <v>170</v>
-      </c>
-      <c r="R85" t="n">
-        <v>1.887253688415304</v>
+        <v>147</v>
       </c>
       <c r="S85" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_SALMONELLOSIS_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO85" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP85" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR85" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS85" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ85" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS85" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_SALMONELLOSIS_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT85" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU85" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV85" t="inlineStr">
         <is>
-          <t>foph_idd</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Switzerland FOPH IDD</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr">
         <is>
-          <t>rest_api</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ85" t="inlineStr">
         <is>
-          <t>foph_idd</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="BA85" t="inlineStr">
         <is>
-          <t>Switzerland FOPH IDD</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="BB85" t="inlineStr">
         <is>
-          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="BC85" t="inlineStr">
         <is>
-          <t>rest_api</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -15537,17 +15548,17 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>CA-ON</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Ontario, Canada</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -15581,22 +15592,39 @@
         </is>
       </c>
       <c r="N86" t="n">
-        <v>52</v>
+        <v>147</v>
       </c>
       <c r="O86" t="n">
-        <v>52</v>
-      </c>
-      <c r="R86" t="n">
-        <v>0.9249807688493514</v>
-      </c>
-      <c r="S86" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>147</v>
       </c>
       <c r="U86" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1200</t>
+          <t>SER_CA_ON_PHO_IDTO_SALMONELLOSIS_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_SALMONELLOSIS_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W86" t="inlineStr">
+        <is>
+          <t>SRC_CA_ON_PHO_IDTO</t>
+        </is>
+      </c>
+      <c r="X86" t="inlineStr">
+        <is>
+          <t>Salmonellosis</t>
+        </is>
+      </c>
+      <c r="Y86" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z86" t="inlineStr">
+        <is>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -15604,6 +15632,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB86" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC86" t="inlineStr">
+        <is>
+          <t>country:CA-ON:national</t>
+        </is>
+      </c>
+      <c r="AD86" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE86" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF86" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG86" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH86" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI86" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ86" t="inlineStr">
+        <is>
+          <t>PHO_IDTO_2026_07</t>
+        </is>
+      </c>
+      <c r="AK86" t="inlineStr">
+        <is>
+          <t>PHO IDTO current-year monthly preliminary salmonellosis notifications; confirmed cases only under the July 2026 technical notes.</t>
+        </is>
+      </c>
+      <c r="AM86" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN86" t="b">
+        <v>1</v>
+      </c>
       <c r="AO86" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -15616,12 +15702,12 @@
       </c>
       <c r="AQ86" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS86" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1200</t>
+          <t>SER_CA_ON_PHO_IDTO_SALMONELLOSIS_MONTHLY</t>
         </is>
       </c>
       <c r="AT86" t="n">
@@ -15629,47 +15715,47 @@
       </c>
       <c r="AU86" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV86" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ86" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="BA86" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="BB86" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="BC86" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -15696,17 +15782,17 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Switzerland</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -15740,170 +15826,81 @@
         </is>
       </c>
       <c r="N87" t="n">
-        <v>52</v>
+        <v>170</v>
       </c>
       <c r="O87" t="n">
-        <v>52</v>
-      </c>
-      <c r="U87" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1200</t>
-        </is>
-      </c>
-      <c r="V87" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1200</t>
-        </is>
-      </c>
-      <c r="W87" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X87" t="inlineStr">
-        <is>
-          <t>Salmonella, other</t>
-        </is>
-      </c>
-      <c r="Y87" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z87" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA87" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB87" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC87" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD87" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE87" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF87" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG87" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH87" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI87" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ87" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK87" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; Residual Salmonella category excluding Typhi and Paratyphi; retain as its own non-additive series.</t>
-        </is>
-      </c>
-      <c r="AM87" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN87" t="b">
-        <v>1</v>
+        <v>170</v>
+      </c>
+      <c r="R87" t="n">
+        <v>1.887253688415304</v>
+      </c>
+      <c r="S87" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO87" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP87" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ87" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AS87" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1200</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR87" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS87" t="inlineStr"/>
       <c r="AT87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU87" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV87" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>foph_idd</t>
         </is>
       </c>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Switzerland FOPH IDD</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>rest_api</t>
         </is>
       </c>
       <c r="AZ87" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>foph_idd</t>
         </is>
       </c>
       <c r="BA87" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Switzerland FOPH IDD</t>
         </is>
       </c>
       <c r="BB87" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
         </is>
       </c>
       <c r="BC87" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>rest_api</t>
         </is>
       </c>
     </row>
@@ -15935,12 +15932,12 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -15974,13 +15971,13 @@
         </is>
       </c>
       <c r="N88" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="O88" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="R88" t="n">
-        <v>0.9375571876716183</v>
+        <v>0.9249807688493514</v>
       </c>
       <c r="S88" t="inlineStr">
         <is>
@@ -15989,7 +15986,7 @@
       </c>
       <c r="U88" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_302_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1200</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -16009,12 +16006,12 @@
       </c>
       <c r="AQ88" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AS88" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_302_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1200</t>
         </is>
       </c>
       <c r="AT88" t="n">
@@ -16022,47 +16019,47 @@
       </c>
       <c r="AU88" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV88" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ88" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA88" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB88" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC88" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -16094,12 +16091,12 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -16133,29 +16130,29 @@
         </is>
       </c>
       <c r="N89" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="O89" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="U89" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_302_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1200</t>
         </is>
       </c>
       <c r="V89" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_302_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1200</t>
         </is>
       </c>
       <c r="W89" t="inlineStr">
         <is>
-          <t>SRC_NO_FHI_MSIS</t>
+          <t>SRC_FI_THL_TTR</t>
         </is>
       </c>
       <c r="X89" t="inlineStr">
         <is>
-          <t>Salmonellose</t>
+          <t>Salmonella, other</t>
         </is>
       </c>
       <c r="Y89" t="inlineStr">
@@ -16180,7 +16177,7 @@
       </c>
       <c r="AC89" t="inlineStr">
         <is>
-          <t>country:NO:national</t>
+          <t>country:FI:national</t>
         </is>
       </c>
       <c r="AD89" t="inlineStr">
@@ -16215,17 +16212,17 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+          <t>FI_THL_TTR_reporting_group</t>
         </is>
       </c>
       <c r="AK89" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+          <t>Finland THL national monthly notification series; Residual Salmonella category excluding Typhi and Paratyphi; retain as its own non-additive series.</t>
         </is>
       </c>
       <c r="AM89" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN89" t="b">
@@ -16243,12 +16240,12 @@
       </c>
       <c r="AQ89" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AS89" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_302_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1200</t>
         </is>
       </c>
       <c r="AT89" t="n">
@@ -16256,47 +16253,47 @@
       </c>
       <c r="AU89" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV89" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ89" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA89" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB89" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC89" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -16328,12 +16325,12 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>NZ</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -16367,13 +16364,13 @@
         </is>
       </c>
       <c r="N90" t="n">
-        <v>72</v>
+        <v>53</v>
       </c>
       <c r="O90" t="n">
-        <v>72</v>
+        <v>53</v>
       </c>
       <c r="R90" t="n">
-        <v>1.361707535859717</v>
+        <v>0.9375571876716183</v>
       </c>
       <c r="S90" t="inlineStr">
         <is>
@@ -16382,7 +16379,7 @@
       </c>
       <c r="U90" t="inlineStr">
         <is>
-          <t>SER_NZ_SALMONELLOSIS_MONTHLY</t>
+          <t>SER_NO_FHI_302_MONTHLY</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -16407,7 +16404,7 @@
       </c>
       <c r="AS90" t="inlineStr">
         <is>
-          <t>SER_NZ_SALMONELLOSIS_MONTHLY</t>
+          <t>SER_NO_FHI_302_MONTHLY</t>
         </is>
       </c>
       <c r="AT90" t="n">
@@ -16420,42 +16417,42 @@
       </c>
       <c r="AV90" t="inlineStr">
         <is>
-          <t>phf_monthly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ90" t="inlineStr">
         <is>
-          <t>phf_monthly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA90" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB90" t="inlineStr">
         <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC90" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -16487,12 +16484,12 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>NZ</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -16526,29 +16523,29 @@
         </is>
       </c>
       <c r="N91" t="n">
-        <v>72</v>
+        <v>53</v>
       </c>
       <c r="O91" t="n">
-        <v>72</v>
+        <v>53</v>
       </c>
       <c r="U91" t="inlineStr">
         <is>
-          <t>SER_NZ_SALMONELLOSIS_MONTHLY</t>
+          <t>SER_NO_FHI_302_MONTHLY</t>
         </is>
       </c>
       <c r="V91" t="inlineStr">
         <is>
-          <t>SER_NZ_SALMONELLOSIS_MONTHLY</t>
+          <t>SER_NO_FHI_302_MONTHLY</t>
         </is>
       </c>
       <c r="W91" t="inlineStr">
         <is>
-          <t>SRC_NZ_PHS</t>
+          <t>SRC_NO_FHI_MSIS</t>
         </is>
       </c>
       <c r="X91" t="inlineStr">
         <is>
-          <t>Salmonellosis</t>
+          <t>Salmonellose</t>
         </is>
       </c>
       <c r="Y91" t="inlineStr">
@@ -16558,7 +16555,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>notification</t>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -16573,7 +16570,7 @@
       </c>
       <c r="AC91" t="inlineStr">
         <is>
-          <t>country:NZ:national</t>
+          <t>country:NO:national</t>
         </is>
       </c>
       <c r="AD91" t="inlineStr">
@@ -16608,17 +16605,17 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>NZ_PHS_current</t>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
         </is>
       </c>
       <c r="AK91" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science monthly salmonellosis notifications.</t>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
         </is>
       </c>
       <c r="AM91" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN91" t="b">
@@ -16641,7 +16638,7 @@
       </c>
       <c r="AS91" t="inlineStr">
         <is>
-          <t>SER_NZ_SALMONELLOSIS_MONTHLY</t>
+          <t>SER_NO_FHI_302_MONTHLY</t>
         </is>
       </c>
       <c r="AT91" t="n">
@@ -16654,42 +16651,42 @@
       </c>
       <c r="AV91" t="inlineStr">
         <is>
-          <t>phf_monthly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ91" t="inlineStr">
         <is>
-          <t>phf_monthly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA91" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB91" t="inlineStr">
         <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC91" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -16721,12 +16718,12 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NZ</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -16760,13 +16757,13 @@
         </is>
       </c>
       <c r="N92" t="n">
-        <v>112</v>
+        <v>72</v>
       </c>
       <c r="O92" t="n">
-        <v>112</v>
+        <v>72</v>
       </c>
       <c r="R92" t="n">
-        <v>1.046626607967735</v>
+        <v>1.361707535859717</v>
       </c>
       <c r="S92" t="inlineStr">
         <is>
@@ -16775,7 +16772,7 @@
       </c>
       <c r="U92" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_SALMONELLA</t>
+          <t>SER_NZ_SALMONELLOSIS_MONTHLY</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -16800,7 +16797,7 @@
       </c>
       <c r="AS92" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_SALMONELLA</t>
+          <t>SER_NZ_SALMONELLOSIS_MONTHLY</t>
         </is>
       </c>
       <c r="AT92" t="n">
@@ -16813,42 +16810,42 @@
       </c>
       <c r="AV92" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ92" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="BA92" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB92" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="BC92" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -16880,12 +16877,12 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NZ</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -16919,29 +16916,29 @@
         </is>
       </c>
       <c r="N93" t="n">
-        <v>112</v>
+        <v>72</v>
       </c>
       <c r="O93" t="n">
-        <v>112</v>
+        <v>72</v>
       </c>
       <c r="U93" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_SALMONELLA</t>
+          <t>SER_NZ_SALMONELLOSIS_MONTHLY</t>
         </is>
       </c>
       <c r="V93" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_SALMONELLA</t>
+          <t>SER_NZ_SALMONELLOSIS_MONTHLY</t>
         </is>
       </c>
       <c r="W93" t="inlineStr">
         <is>
-          <t>SRC_SE_FOHM_SMINET</t>
+          <t>SRC_NZ_PHS</t>
         </is>
       </c>
       <c r="X93" t="inlineStr">
         <is>
-          <t>Salmonellainfektion</t>
+          <t>Salmonellosis</t>
         </is>
       </c>
       <c r="Y93" t="inlineStr">
@@ -16951,7 +16948,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -16966,7 +16963,7 @@
       </c>
       <c r="AC93" t="inlineStr">
         <is>
-          <t>country:SE:national</t>
+          <t>country:NZ:national</t>
         </is>
       </c>
       <c r="AD93" t="inlineStr">
@@ -17001,17 +16998,17 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>SE_FOHM_SMINET_current</t>
+          <t>NZ_PHS_current</t>
         </is>
       </c>
       <c r="AK93" t="inlineStr">
         <is>
-          <t>Sweden FHM SmiNet national monthly notification series; Retain FHM source scope alongside separate Typhi and Paratyphi categories.</t>
+          <t>New Zealand PHF Science monthly salmonellosis notifications.</t>
         </is>
       </c>
       <c r="AM93" t="inlineStr">
         <is>
-          <t>revised</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN93" t="b">
@@ -17034,7 +17031,7 @@
       </c>
       <c r="AS93" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_SALMONELLA</t>
+          <t>SER_NZ_SALMONELLOSIS_MONTHLY</t>
         </is>
       </c>
       <c r="AT93" t="n">
@@ -17047,42 +17044,42 @@
       </c>
       <c r="AV93" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ93" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="BA93" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB93" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="BC93" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -17114,12 +17111,12 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -17144,7 +17141,7 @@
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="M94" t="inlineStr">
@@ -17153,81 +17150,95 @@
         </is>
       </c>
       <c r="N94" t="n">
-        <v>633</v>
+        <v>112</v>
       </c>
       <c r="O94" t="n">
-        <v>633</v>
+        <v>112</v>
       </c>
       <c r="R94" t="n">
-        <v>0.1813569138043021</v>
+        <v>1.046626607967735</v>
       </c>
       <c r="S94" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U94" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_SALMONELLA</t>
+        </is>
+      </c>
+      <c r="AA94" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO94" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP94" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR94" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS94" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ94" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS94" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_SALMONELLA</t>
+        </is>
+      </c>
       <c r="AT94" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU94" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV94" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ94" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA94" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB94" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC94" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -17254,17 +17265,17 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -17289,7 +17300,7 @@
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="M95" t="inlineStr">
@@ -17298,81 +17309,170 @@
         </is>
       </c>
       <c r="N95" t="n">
-        <v>611</v>
+        <v>112</v>
       </c>
       <c r="O95" t="n">
-        <v>611</v>
-      </c>
-      <c r="R95" t="n">
-        <v>0.1750538299122094</v>
-      </c>
-      <c r="S95" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>112</v>
+      </c>
+      <c r="U95" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_SALMONELLA</t>
+        </is>
+      </c>
+      <c r="V95" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_SALMONELLA</t>
+        </is>
+      </c>
+      <c r="W95" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X95" t="inlineStr">
+        <is>
+          <t>Salmonellainfektion</t>
+        </is>
+      </c>
+      <c r="Y95" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z95" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA95" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB95" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC95" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD95" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE95" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF95" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG95" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH95" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI95" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ95" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK95" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; Retain FHM source scope alongside separate Typhi and Paratyphi categories.</t>
+        </is>
+      </c>
+      <c r="AM95" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN95" t="b">
+        <v>1</v>
       </c>
       <c r="AO95" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP95" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR95" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS95" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ95" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS95" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_SALMONELLA</t>
+        </is>
+      </c>
       <c r="AT95" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU95" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV95" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ95" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA95" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB95" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC95" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -17434,7 +17534,7 @@
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="M96" t="inlineStr">
@@ -17443,13 +17543,13 @@
         </is>
       </c>
       <c r="N96" t="n">
-        <v>626</v>
+        <v>633</v>
       </c>
       <c r="O96" t="n">
-        <v>626</v>
+        <v>633</v>
       </c>
       <c r="R96" t="n">
-        <v>0.1793513871113635</v>
+        <v>0.1813569138043021</v>
       </c>
       <c r="S96" t="inlineStr">
         <is>
@@ -17579,7 +17679,7 @@
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="M97" t="inlineStr">
@@ -17588,13 +17688,13 @@
         </is>
       </c>
       <c r="N97" t="n">
-        <v>651</v>
+        <v>611</v>
       </c>
       <c r="O97" t="n">
-        <v>651</v>
+        <v>611</v>
       </c>
       <c r="R97" t="n">
-        <v>0.186513982443287</v>
+        <v>0.1750538299122094</v>
       </c>
       <c r="S97" t="inlineStr">
         <is>
@@ -17694,12 +17794,12 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -17724,22 +17824,22 @@
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="N98" t="n">
-        <v>714</v>
+        <v>626</v>
       </c>
       <c r="O98" t="n">
-        <v>714</v>
+        <v>626</v>
       </c>
       <c r="R98" t="n">
-        <v>2.62238763913713</v>
+        <v>0.1793513871113635</v>
       </c>
       <c r="S98" t="inlineStr">
         <is>
@@ -17772,42 +17872,42 @@
       </c>
       <c r="AV98" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ98" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA98" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB98" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC98" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -17839,12 +17939,12 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>CH</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -17869,22 +17969,22 @@
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="N99" t="n">
-        <v>290</v>
+        <v>651</v>
       </c>
       <c r="O99" t="n">
-        <v>290</v>
+        <v>651</v>
       </c>
       <c r="R99" t="n">
-        <v>3.219432762590813</v>
+        <v>0.186513982443287</v>
       </c>
       <c r="S99" t="inlineStr">
         <is>
@@ -17917,42 +18017,42 @@
       </c>
       <c r="AV99" t="inlineStr">
         <is>
-          <t>foph_idd</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Switzerland FOPH IDD</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr">
         <is>
-          <t>rest_api</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ99" t="inlineStr">
         <is>
-          <t>foph_idd</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA99" t="inlineStr">
         <is>
-          <t>Switzerland FOPH IDD</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB99" t="inlineStr">
         <is>
-          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC99" t="inlineStr">
         <is>
-          <t>rest_api</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -17984,12 +18084,12 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -18023,95 +18123,81 @@
         </is>
       </c>
       <c r="N100" t="n">
-        <v>68</v>
+        <v>714</v>
       </c>
       <c r="O100" t="n">
-        <v>68</v>
+        <v>714</v>
       </c>
       <c r="R100" t="n">
-        <v>1.209590236187614</v>
+        <v>2.62238763913713</v>
       </c>
       <c r="S100" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U100" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1200</t>
-        </is>
-      </c>
-      <c r="AA100" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO100" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP100" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ100" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AS100" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1200</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR100" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS100" t="inlineStr"/>
       <c r="AT100" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU100" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV100" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ100" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA100" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB100" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC100" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -18138,17 +18224,17 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Switzerland</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -18182,170 +18268,81 @@
         </is>
       </c>
       <c r="N101" t="n">
-        <v>68</v>
+        <v>290</v>
       </c>
       <c r="O101" t="n">
-        <v>68</v>
-      </c>
-      <c r="U101" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1200</t>
-        </is>
-      </c>
-      <c r="V101" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1200</t>
-        </is>
-      </c>
-      <c r="W101" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>Salmonella, other</t>
-        </is>
-      </c>
-      <c r="Y101" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z101" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA101" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB101" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC101" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD101" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE101" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF101" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG101" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH101" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI101" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ101" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK101" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; Residual Salmonella category excluding Typhi and Paratyphi; retain as its own non-additive series.</t>
-        </is>
-      </c>
-      <c r="AM101" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN101" t="b">
-        <v>1</v>
+        <v>290</v>
+      </c>
+      <c r="R101" t="n">
+        <v>3.219432762590813</v>
+      </c>
+      <c r="S101" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO101" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP101" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ101" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AS101" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1200</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR101" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS101" t="inlineStr"/>
       <c r="AT101" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU101" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV101" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>foph_idd</t>
         </is>
       </c>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Switzerland FOPH IDD</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>rest_api</t>
         </is>
       </c>
       <c r="AZ101" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>foph_idd</t>
         </is>
       </c>
       <c r="BA101" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Switzerland FOPH IDD</t>
         </is>
       </c>
       <c r="BB101" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
         </is>
       </c>
       <c r="BC101" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>rest_api</t>
         </is>
       </c>
     </row>
@@ -18377,12 +18374,12 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -18416,13 +18413,13 @@
         </is>
       </c>
       <c r="N102" t="n">
-        <v>112</v>
+        <v>68</v>
       </c>
       <c r="O102" t="n">
-        <v>112</v>
+        <v>68</v>
       </c>
       <c r="R102" t="n">
-        <v>1.981252924890967</v>
+        <v>1.209590236187614</v>
       </c>
       <c r="S102" t="inlineStr">
         <is>
@@ -18431,7 +18428,7 @@
       </c>
       <c r="U102" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_302_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1200</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -18451,12 +18448,12 @@
       </c>
       <c r="AQ102" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AS102" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_302_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1200</t>
         </is>
       </c>
       <c r="AT102" t="n">
@@ -18464,47 +18461,47 @@
       </c>
       <c r="AU102" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV102" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ102" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA102" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB102" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC102" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -18536,12 +18533,12 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -18575,29 +18572,29 @@
         </is>
       </c>
       <c r="N103" t="n">
-        <v>112</v>
+        <v>68</v>
       </c>
       <c r="O103" t="n">
-        <v>112</v>
+        <v>68</v>
       </c>
       <c r="U103" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_302_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1200</t>
         </is>
       </c>
       <c r="V103" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_302_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1200</t>
         </is>
       </c>
       <c r="W103" t="inlineStr">
         <is>
-          <t>SRC_NO_FHI_MSIS</t>
+          <t>SRC_FI_THL_TTR</t>
         </is>
       </c>
       <c r="X103" t="inlineStr">
         <is>
-          <t>Salmonellose</t>
+          <t>Salmonella, other</t>
         </is>
       </c>
       <c r="Y103" t="inlineStr">
@@ -18622,7 +18619,7 @@
       </c>
       <c r="AC103" t="inlineStr">
         <is>
-          <t>country:NO:national</t>
+          <t>country:FI:national</t>
         </is>
       </c>
       <c r="AD103" t="inlineStr">
@@ -18657,17 +18654,17 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+          <t>FI_THL_TTR_reporting_group</t>
         </is>
       </c>
       <c r="AK103" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+          <t>Finland THL national monthly notification series; Residual Salmonella category excluding Typhi and Paratyphi; retain as its own non-additive series.</t>
         </is>
       </c>
       <c r="AM103" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN103" t="b">
@@ -18685,12 +18682,12 @@
       </c>
       <c r="AQ103" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AS103" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_302_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1200</t>
         </is>
       </c>
       <c r="AT103" t="n">
@@ -18698,47 +18695,47 @@
       </c>
       <c r="AU103" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV103" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ103" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA103" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB103" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC103" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -18770,12 +18767,12 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -18809,13 +18806,13 @@
         </is>
       </c>
       <c r="N104" t="n">
-        <v>142</v>
+        <v>112</v>
       </c>
       <c r="O104" t="n">
-        <v>142</v>
+        <v>112</v>
       </c>
       <c r="R104" t="n">
-        <v>1.326973020816235</v>
+        <v>1.981252924890967</v>
       </c>
       <c r="S104" t="inlineStr">
         <is>
@@ -18824,7 +18821,7 @@
       </c>
       <c r="U104" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_SALMONELLA</t>
+          <t>SER_NO_FHI_302_MONTHLY</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -18849,7 +18846,7 @@
       </c>
       <c r="AS104" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_SALMONELLA</t>
+          <t>SER_NO_FHI_302_MONTHLY</t>
         </is>
       </c>
       <c r="AT104" t="n">
@@ -18862,42 +18859,42 @@
       </c>
       <c r="AV104" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ104" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA104" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB104" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC104" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -18929,12 +18926,12 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -18968,29 +18965,29 @@
         </is>
       </c>
       <c r="N105" t="n">
-        <v>142</v>
+        <v>112</v>
       </c>
       <c r="O105" t="n">
-        <v>142</v>
+        <v>112</v>
       </c>
       <c r="U105" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_SALMONELLA</t>
+          <t>SER_NO_FHI_302_MONTHLY</t>
         </is>
       </c>
       <c r="V105" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_SALMONELLA</t>
+          <t>SER_NO_FHI_302_MONTHLY</t>
         </is>
       </c>
       <c r="W105" t="inlineStr">
         <is>
-          <t>SRC_SE_FOHM_SMINET</t>
+          <t>SRC_NO_FHI_MSIS</t>
         </is>
       </c>
       <c r="X105" t="inlineStr">
         <is>
-          <t>Salmonellainfektion</t>
+          <t>Salmonellose</t>
         </is>
       </c>
       <c r="Y105" t="inlineStr">
@@ -19015,7 +19012,7 @@
       </c>
       <c r="AC105" t="inlineStr">
         <is>
-          <t>country:SE:national</t>
+          <t>country:NO:national</t>
         </is>
       </c>
       <c r="AD105" t="inlineStr">
@@ -19050,17 +19047,17 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>SE_FOHM_SMINET_current</t>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
         </is>
       </c>
       <c r="AK105" t="inlineStr">
         <is>
-          <t>Sweden FHM SmiNet national monthly notification series; Retain FHM source scope alongside separate Typhi and Paratyphi categories.</t>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
         </is>
       </c>
       <c r="AM105" t="inlineStr">
         <is>
-          <t>revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN105" t="b">
@@ -19083,7 +19080,7 @@
       </c>
       <c r="AS105" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_SALMONELLA</t>
+          <t>SER_NO_FHI_302_MONTHLY</t>
         </is>
       </c>
       <c r="AT105" t="n">
@@ -19096,42 +19093,42 @@
       </c>
       <c r="AV105" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ105" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA105" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB105" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC105" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -19163,12 +19160,12 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -19193,7 +19190,7 @@
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M106" t="inlineStr">
@@ -19202,81 +19199,95 @@
         </is>
       </c>
       <c r="N106" t="n">
-        <v>671</v>
+        <v>142</v>
       </c>
       <c r="O106" t="n">
-        <v>671</v>
+        <v>142</v>
       </c>
       <c r="R106" t="n">
-        <v>0.1922440587088257</v>
+        <v>1.326973020816235</v>
       </c>
       <c r="S106" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U106" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_SALMONELLA</t>
+        </is>
+      </c>
+      <c r="AA106" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO106" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP106" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR106" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS106" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ106" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS106" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_SALMONELLA</t>
+        </is>
+      </c>
       <c r="AT106" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU106" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV106" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ106" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA106" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB106" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC106" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -19303,17 +19314,17 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -19338,7 +19349,7 @@
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M107" t="inlineStr">
@@ -19347,81 +19358,170 @@
         </is>
       </c>
       <c r="N107" t="n">
-        <v>839</v>
+        <v>142</v>
       </c>
       <c r="O107" t="n">
-        <v>839</v>
-      </c>
-      <c r="R107" t="n">
-        <v>0.2403766993393514</v>
-      </c>
-      <c r="S107" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>142</v>
+      </c>
+      <c r="U107" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_SALMONELLA</t>
+        </is>
+      </c>
+      <c r="V107" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_SALMONELLA</t>
+        </is>
+      </c>
+      <c r="W107" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X107" t="inlineStr">
+        <is>
+          <t>Salmonellainfektion</t>
+        </is>
+      </c>
+      <c r="Y107" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z107" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA107" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB107" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC107" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD107" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE107" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF107" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG107" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH107" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI107" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ107" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK107" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; Retain FHM source scope alongside separate Typhi and Paratyphi categories.</t>
+        </is>
+      </c>
+      <c r="AM107" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN107" t="b">
+        <v>1</v>
       </c>
       <c r="AO107" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP107" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR107" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS107" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ107" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS107" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_SALMONELLA</t>
+        </is>
+      </c>
       <c r="AT107" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU107" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV107" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ107" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA107" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB107" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC107" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -19483,7 +19583,7 @@
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="M108" t="inlineStr">
@@ -19492,13 +19592,13 @@
         </is>
       </c>
       <c r="N108" t="n">
-        <v>1110</v>
+        <v>671</v>
       </c>
       <c r="O108" t="n">
-        <v>1110</v>
+        <v>671</v>
       </c>
       <c r="R108" t="n">
-        <v>0.3180192327374018</v>
+        <v>0.1922440587088257</v>
       </c>
       <c r="S108" t="inlineStr">
         <is>
@@ -19628,7 +19728,7 @@
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="M109" t="inlineStr">
@@ -19637,13 +19737,13 @@
         </is>
       </c>
       <c r="N109" t="n">
-        <v>1115</v>
+        <v>839</v>
       </c>
       <c r="O109" t="n">
-        <v>1115</v>
+        <v>839</v>
       </c>
       <c r="R109" t="n">
-        <v>0.3194517518037865</v>
+        <v>0.2403766993393514</v>
       </c>
       <c r="S109" t="inlineStr">
         <is>
@@ -19743,12 +19843,12 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -19773,22 +19873,22 @@
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="M110" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N110" t="n">
-        <v>241</v>
+        <v>1110</v>
       </c>
       <c r="O110" t="n">
-        <v>241</v>
+        <v>1110</v>
       </c>
       <c r="R110" t="n">
-        <v>0.8851476485042695</v>
+        <v>0.3180192327374018</v>
       </c>
       <c r="S110" t="inlineStr">
         <is>
@@ -19821,42 +19921,42 @@
       </c>
       <c r="AV110" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ110" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA110" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB110" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC110" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -19888,12 +19988,12 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -19918,104 +20018,90 @@
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="M111" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N111" t="n">
-        <v>15</v>
+        <v>1115</v>
       </c>
       <c r="O111" t="n">
-        <v>15</v>
+        <v>1115</v>
       </c>
       <c r="R111" t="n">
-        <v>0.2668213756296206</v>
+        <v>0.3194517518037865</v>
       </c>
       <c r="S111" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U111" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1200</t>
-        </is>
-      </c>
-      <c r="AA111" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO111" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP111" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ111" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AS111" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1200</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR111" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS111" t="inlineStr"/>
       <c r="AT111" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU111" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV111" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ111" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA111" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB111" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC111" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -20042,17 +20128,17 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -20086,170 +20172,81 @@
         </is>
       </c>
       <c r="N112" t="n">
-        <v>15</v>
+        <v>276</v>
       </c>
       <c r="O112" t="n">
-        <v>15</v>
-      </c>
-      <c r="U112" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1200</t>
-        </is>
-      </c>
-      <c r="V112" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1200</t>
-        </is>
-      </c>
-      <c r="W112" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X112" t="inlineStr">
-        <is>
-          <t>Salmonella, other</t>
-        </is>
-      </c>
-      <c r="Y112" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z112" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA112" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB112" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC112" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD112" t="inlineStr">
+        <v>276</v>
+      </c>
+      <c r="R112" t="n">
+        <v>1.013696062187462</v>
+      </c>
+      <c r="S112" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO112" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP112" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR112" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS112" t="inlineStr"/>
+      <c r="AT112" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU112" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV112" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="AE112" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF112" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG112" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH112" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI112" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ112" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK112" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; Residual Salmonella category excluding Typhi and Paratyphi; retain as its own non-additive series.</t>
-        </is>
-      </c>
-      <c r="AM112" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN112" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO112" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP112" t="inlineStr">
-        <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ112" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AS112" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1200</t>
-        </is>
-      </c>
-      <c r="AT112" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU112" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
-        </is>
-      </c>
-      <c r="AV112" t="inlineStr">
-        <is>
-          <t>thl_ttr</t>
-        </is>
-      </c>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ112" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA112" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB112" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC112" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -20281,12 +20278,12 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -20320,13 +20317,13 @@
         </is>
       </c>
       <c r="N113" t="n">
-        <v>44</v>
+        <v>15</v>
       </c>
       <c r="O113" t="n">
-        <v>44</v>
+        <v>15</v>
       </c>
       <c r="R113" t="n">
-        <v>0.7783493633500227</v>
+        <v>0.2668213756296206</v>
       </c>
       <c r="S113" t="inlineStr">
         <is>
@@ -20335,7 +20332,7 @@
       </c>
       <c r="U113" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_302_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1200</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
@@ -20355,12 +20352,12 @@
       </c>
       <c r="AQ113" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AS113" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_302_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1200</t>
         </is>
       </c>
       <c r="AT113" t="n">
@@ -20368,47 +20365,47 @@
       </c>
       <c r="AU113" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV113" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ113" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA113" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB113" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC113" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -20440,12 +20437,12 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -20479,29 +20476,29 @@
         </is>
       </c>
       <c r="N114" t="n">
-        <v>44</v>
+        <v>15</v>
       </c>
       <c r="O114" t="n">
-        <v>44</v>
+        <v>15</v>
       </c>
       <c r="U114" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_302_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1200</t>
         </is>
       </c>
       <c r="V114" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_302_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1200</t>
         </is>
       </c>
       <c r="W114" t="inlineStr">
         <is>
-          <t>SRC_NO_FHI_MSIS</t>
+          <t>SRC_FI_THL_TTR</t>
         </is>
       </c>
       <c r="X114" t="inlineStr">
         <is>
-          <t>Salmonellose</t>
+          <t>Salmonella, other</t>
         </is>
       </c>
       <c r="Y114" t="inlineStr">
@@ -20526,7 +20523,7 @@
       </c>
       <c r="AC114" t="inlineStr">
         <is>
-          <t>country:NO:national</t>
+          <t>country:FI:national</t>
         </is>
       </c>
       <c r="AD114" t="inlineStr">
@@ -20561,17 +20558,17 @@
       </c>
       <c r="AJ114" t="inlineStr">
         <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+          <t>FI_THL_TTR_reporting_group</t>
         </is>
       </c>
       <c r="AK114" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+          <t>Finland THL national monthly notification series; Residual Salmonella category excluding Typhi and Paratyphi; retain as its own non-additive series.</t>
         </is>
       </c>
       <c r="AM114" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN114" t="b">
@@ -20589,12 +20586,12 @@
       </c>
       <c r="AQ114" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AS114" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_302_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1200</t>
         </is>
       </c>
       <c r="AT114" t="n">
@@ -20602,47 +20599,47 @@
       </c>
       <c r="AU114" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV114" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ114" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA114" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB114" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC114" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -20674,12 +20671,12 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -20713,81 +20710,95 @@
         </is>
       </c>
       <c r="N115" t="n">
-        <v>1166</v>
+        <v>44</v>
       </c>
       <c r="O115" t="n">
-        <v>1166</v>
+        <v>44</v>
       </c>
       <c r="R115" t="n">
-        <v>0.3340634462809103</v>
+        <v>0.7783493633500227</v>
       </c>
       <c r="S115" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U115" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_302_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA115" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO115" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP115" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR115" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS115" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ115" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS115" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_302_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT115" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU115" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV115" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ115" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA115" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB115" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC115" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -20814,123 +20825,502 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>D114</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>Salmonellosis</t>
+        </is>
+      </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>沙门氏菌病</t>
+        </is>
+      </c>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L116" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M116" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N116" t="n">
+        <v>44</v>
+      </c>
+      <c r="O116" t="n">
+        <v>44</v>
+      </c>
+      <c r="U116" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_302_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V116" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_302_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W116" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X116" t="inlineStr">
+        <is>
+          <t>Salmonellose</t>
+        </is>
+      </c>
+      <c r="Y116" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z116" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA116" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB116" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC116" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD116" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE116" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF116" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG116" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH116" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI116" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ116" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK116" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM116" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN116" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO116" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP116" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ116" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS116" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_302_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT116" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU116" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV116" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW116" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX116" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY116" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ116" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA116" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB116" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC116" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>D114</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>salmonellosis</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>Salmonellosis</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
           <t>public_projection</t>
         </is>
       </c>
-      <c r="F116" t="inlineStr">
+      <c r="F117" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="G116" t="inlineStr">
+      <c r="G117" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
       </c>
-      <c r="H116" t="inlineStr">
-        <is>
-          <t>D114</t>
-        </is>
-      </c>
-      <c r="I116" t="inlineStr">
-        <is>
-          <t>Salmonellosis</t>
-        </is>
-      </c>
-      <c r="J116" t="inlineStr">
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>D114</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>Salmonellosis</t>
+        </is>
+      </c>
+      <c r="J117" t="inlineStr">
         <is>
           <t>沙门氏菌病</t>
         </is>
       </c>
-      <c r="K116" t="inlineStr">
+      <c r="K117" t="inlineStr">
         <is>
           <t>Bacterial</t>
         </is>
       </c>
-      <c r="L116" t="inlineStr">
+      <c r="L117" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N117" t="n">
+        <v>1166</v>
+      </c>
+      <c r="O117" t="n">
+        <v>1166</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0.3340634462809103</v>
+      </c>
+      <c r="S117" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO117" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP117" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR117" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS117" t="inlineStr"/>
+      <c r="AT117" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU117" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV117" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW117" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX117" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY117" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ117" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA117" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB117" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC117" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>D114</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>salmonellosis</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>Salmonellosis</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>D114</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>Salmonellosis</t>
+        </is>
+      </c>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>沙门氏菌病</t>
+        </is>
+      </c>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L118" t="inlineStr">
         <is>
           <t>2026-08-08</t>
         </is>
       </c>
-      <c r="M116" t="inlineStr">
+      <c r="M118" t="inlineStr">
         <is>
           <t>2026-08</t>
         </is>
       </c>
-      <c r="N116" t="n">
+      <c r="N118" t="n">
         <v>1060</v>
       </c>
-      <c r="O116" t="n">
+      <c r="O118" t="n">
         <v>1060</v>
       </c>
-      <c r="R116" t="n">
+      <c r="R118" t="n">
         <v>0.3036940420735548</v>
       </c>
-      <c r="S116" t="inlineStr">
+      <c r="S118" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AO116" t="inlineStr">
+      <c r="AO118" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
         </is>
       </c>
-      <c r="AP116" t="inlineStr">
+      <c r="AP118" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
         </is>
       </c>
-      <c r="AR116" t="inlineStr">
+      <c r="AR118" t="inlineStr">
         <is>
           <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
-      <c r="AS116" t="inlineStr"/>
-      <c r="AT116" t="n">
+      <c r="AS118" t="inlineStr"/>
+      <c r="AT118" t="n">
         <v>0</v>
       </c>
-      <c r="AU116" t="inlineStr">
+      <c r="AU118" t="inlineStr">
         <is>
           <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
-      <c r="AV116" t="inlineStr">
+      <c r="AV118" t="inlineStr">
         <is>
           <t>nndss_api</t>
         </is>
       </c>
-      <c r="AW116" t="inlineStr">
+      <c r="AW118" t="inlineStr">
         <is>
           <t>US CDC NNDSS</t>
         </is>
       </c>
-      <c r="AX116" t="inlineStr">
+      <c r="AX118" t="inlineStr">
         <is>
           <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
-      <c r="AY116" t="inlineStr">
+      <c r="AY118" t="inlineStr">
         <is>
           <t>api</t>
         </is>
       </c>
-      <c r="AZ116" t="inlineStr">
+      <c r="AZ118" t="inlineStr">
         <is>
           <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
-      <c r="BA116" t="inlineStr">
+      <c r="BA118" t="inlineStr">
         <is>
           <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
-      <c r="BB116" t="inlineStr">
+      <c r="BB118" t="inlineStr">
         <is>
           <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
-      <c r="BC116" t="inlineStr">
+      <c r="BC118" t="inlineStr">
         <is>
           <t>api; api</t>
         </is>
@@ -21052,7 +21442,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="10">
@@ -21062,7 +21452,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>115</v>
+        <v>117</v>
       </c>
     </row>
     <row r="11">
@@ -21082,7 +21472,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="13">
@@ -21114,7 +21504,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>28418</v>
+        <v>28607</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d114/2026-2029.xlsx
+++ b/diseases/d114/2026-2029.xlsx
@@ -18123,13 +18123,13 @@
         </is>
       </c>
       <c r="N100" t="n">
-        <v>714</v>
+        <v>716</v>
       </c>
       <c r="O100" t="n">
-        <v>714</v>
+        <v>716</v>
       </c>
       <c r="R100" t="n">
-        <v>2.62238763913713</v>
+        <v>2.62973326277617</v>
       </c>
       <c r="S100" t="inlineStr">
         <is>
@@ -20172,13 +20172,13 @@
         </is>
       </c>
       <c r="N112" t="n">
-        <v>276</v>
+        <v>295</v>
       </c>
       <c r="O112" t="n">
-        <v>276</v>
+        <v>295</v>
       </c>
       <c r="R112" t="n">
-        <v>1.013696062187462</v>
+        <v>1.083479486758338</v>
       </c>
       <c r="S112" t="inlineStr">
         <is>
@@ -20317,13 +20317,13 @@
         </is>
       </c>
       <c r="N113" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="O113" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="R113" t="n">
-        <v>0.2668213756296206</v>
+        <v>0.3201856507555447</v>
       </c>
       <c r="S113" t="inlineStr">
         <is>
@@ -20476,10 +20476,10 @@
         </is>
       </c>
       <c r="N114" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="O114" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="U114" t="inlineStr">
         <is>
@@ -21504,7 +21504,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>28607</v>
+        <v>28631</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d114/2026-2029.xlsx
+++ b/diseases/d114/2026-2029.xlsx
@@ -20317,13 +20317,13 @@
         </is>
       </c>
       <c r="N113" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="O113" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="R113" t="n">
-        <v>0.3201856507555447</v>
+        <v>0.3557618341728275</v>
       </c>
       <c r="S113" t="inlineStr">
         <is>
@@ -20476,10 +20476,10 @@
         </is>
       </c>
       <c r="N114" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="O114" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="U114" t="inlineStr">
         <is>
@@ -21504,7 +21504,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>28631</v>
+        <v>28633</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d114/2026-2029.xlsx
+++ b/diseases/d114/2026-2029.xlsx
@@ -18123,13 +18123,13 @@
         </is>
       </c>
       <c r="N100" t="n">
-        <v>716</v>
+        <v>720</v>
       </c>
       <c r="O100" t="n">
-        <v>716</v>
+        <v>720</v>
       </c>
       <c r="R100" t="n">
-        <v>2.62973326277617</v>
+        <v>2.644424510054249</v>
       </c>
       <c r="S100" t="inlineStr">
         <is>
@@ -18413,13 +18413,13 @@
         </is>
       </c>
       <c r="N102" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="O102" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="R102" t="n">
-        <v>1.209590236187614</v>
+        <v>1.191802144478972</v>
       </c>
       <c r="S102" t="inlineStr">
         <is>
@@ -18572,10 +18572,10 @@
         </is>
       </c>
       <c r="N103" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="O103" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="U103" t="inlineStr">
         <is>
@@ -20172,13 +20172,13 @@
         </is>
       </c>
       <c r="N112" t="n">
-        <v>295</v>
+        <v>353</v>
       </c>
       <c r="O112" t="n">
-        <v>295</v>
+        <v>353</v>
       </c>
       <c r="R112" t="n">
-        <v>1.083479486758338</v>
+        <v>1.296502572290486</v>
       </c>
       <c r="S112" t="inlineStr">
         <is>
@@ -20317,13 +20317,13 @@
         </is>
       </c>
       <c r="N113" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="O113" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="R113" t="n">
-        <v>0.3557618341728275</v>
+        <v>0.3913380175901103</v>
       </c>
       <c r="S113" t="inlineStr">
         <is>
@@ -20476,10 +20476,10 @@
         </is>
       </c>
       <c r="N114" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="O114" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="U114" t="inlineStr">
         <is>
@@ -20710,13 +20710,13 @@
         </is>
       </c>
       <c r="N115" t="n">
-        <v>44</v>
+        <v>72</v>
       </c>
       <c r="O115" t="n">
-        <v>44</v>
+        <v>72</v>
       </c>
       <c r="R115" t="n">
-        <v>0.7783493633500227</v>
+        <v>1.273662594572764</v>
       </c>
       <c r="S115" t="inlineStr">
         <is>
@@ -20869,10 +20869,10 @@
         </is>
       </c>
       <c r="N116" t="n">
-        <v>44</v>
+        <v>72</v>
       </c>
       <c r="O116" t="n">
-        <v>44</v>
+        <v>72</v>
       </c>
       <c r="U116" t="inlineStr">
         <is>
@@ -21321,6 +21321,151 @@
         </is>
       </c>
       <c r="BC118" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>D114</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>salmonellosis</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>Salmonellosis</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>D114</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>Salmonellosis</t>
+        </is>
+      </c>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>沙门氏菌病</t>
+        </is>
+      </c>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L119" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N119" t="n">
+        <v>1056</v>
+      </c>
+      <c r="O119" t="n">
+        <v>1056</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0.3025480268204471</v>
+      </c>
+      <c r="S119" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO119" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP119" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR119" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS119" t="inlineStr"/>
+      <c r="AT119" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU119" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV119" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW119" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX119" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY119" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ119" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA119" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB119" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC119" t="inlineStr">
         <is>
           <t>api; api</t>
         </is>
@@ -21359,7 +21504,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
@@ -21442,7 +21587,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="10">
@@ -21452,7 +21597,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="11">
@@ -21504,7 +21649,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>28633</v>
+        <v>29780</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d114/2026-2029.xlsx
+++ b/diseases/d114/2026-2029.xlsx
@@ -20172,13 +20172,13 @@
         </is>
       </c>
       <c r="N112" t="n">
-        <v>353</v>
+        <v>382</v>
       </c>
       <c r="O112" t="n">
-        <v>353</v>
+        <v>382</v>
       </c>
       <c r="R112" t="n">
-        <v>1.296502572290486</v>
+        <v>1.40301411505656</v>
       </c>
       <c r="S112" t="inlineStr">
         <is>
@@ -20317,13 +20317,13 @@
         </is>
       </c>
       <c r="N113" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="O113" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="R113" t="n">
-        <v>0.3913380175901103</v>
+        <v>0.4091261092987516</v>
       </c>
       <c r="S113" t="inlineStr">
         <is>
@@ -20476,10 +20476,10 @@
         </is>
       </c>
       <c r="N114" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="O114" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="U114" t="inlineStr">
         <is>
@@ -21649,7 +21649,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>29780</v>
+        <v>29810</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d114/2026-2029.xlsx
+++ b/diseases/d114/2026-2029.xlsx
@@ -20172,13 +20172,13 @@
         </is>
       </c>
       <c r="N112" t="n">
-        <v>382</v>
+        <v>399</v>
       </c>
       <c r="O112" t="n">
-        <v>382</v>
+        <v>399</v>
       </c>
       <c r="R112" t="n">
-        <v>1.40301411505656</v>
+        <v>1.465451915988396</v>
       </c>
       <c r="S112" t="inlineStr">
         <is>
@@ -20317,13 +20317,13 @@
         </is>
       </c>
       <c r="N113" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="O113" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="R113" t="n">
-        <v>0.4091261092987516</v>
+        <v>0.4802784761333171</v>
       </c>
       <c r="S113" t="inlineStr">
         <is>
@@ -20476,10 +20476,10 @@
         </is>
       </c>
       <c r="N114" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="O114" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="U114" t="inlineStr">
         <is>
@@ -21649,7 +21649,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>29810</v>
+        <v>29831</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d114/2026-2029.xlsx
+++ b/diseases/d114/2026-2029.xlsx
@@ -20172,13 +20172,13 @@
         </is>
       </c>
       <c r="N112" t="n">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="O112" t="n">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="R112" t="n">
-        <v>1.465451915988396</v>
+        <v>1.476470351446956</v>
       </c>
       <c r="S112" t="inlineStr">
         <is>
@@ -21649,7 +21649,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>29831</v>
+        <v>29834</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d114/2026-2029.xlsx
+++ b/diseases/d114/2026-2029.xlsx
@@ -18123,13 +18123,13 @@
         </is>
       </c>
       <c r="N100" t="n">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="O100" t="n">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="R100" t="n">
-        <v>2.644424510054249</v>
+        <v>2.648097321873768</v>
       </c>
       <c r="S100" t="inlineStr">
         <is>
@@ -20172,13 +20172,13 @@
         </is>
       </c>
       <c r="N112" t="n">
-        <v>402</v>
+        <v>431</v>
       </c>
       <c r="O112" t="n">
-        <v>402</v>
+        <v>431</v>
       </c>
       <c r="R112" t="n">
-        <v>1.476470351446956</v>
+        <v>1.58298189421303</v>
       </c>
       <c r="S112" t="inlineStr">
         <is>
@@ -21649,7 +21649,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>29834</v>
+        <v>29864</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d114/2026-2029.xlsx
+++ b/diseases/d114/2026-2029.xlsx
@@ -15291,13 +15291,13 @@
         </is>
       </c>
       <c r="N84" t="n">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="O84" t="n">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="R84" t="n">
-        <v>2.813373853752159</v>
+        <v>2.817046665571679</v>
       </c>
       <c r="S84" t="inlineStr">
         <is>
@@ -16757,13 +16757,13 @@
         </is>
       </c>
       <c r="N92" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="O92" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="R92" t="n">
-        <v>1.361707535859717</v>
+        <v>1.342794931194999</v>
       </c>
       <c r="S92" t="inlineStr">
         <is>
@@ -16916,10 +16916,10 @@
         </is>
       </c>
       <c r="N93" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="O93" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="U93" t="inlineStr">
         <is>
@@ -18123,13 +18123,13 @@
         </is>
       </c>
       <c r="N100" t="n">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="O100" t="n">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="R100" t="n">
-        <v>2.648097321873768</v>
+        <v>2.651770133693288</v>
       </c>
       <c r="S100" t="inlineStr">
         <is>
@@ -19160,12 +19160,12 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NZ</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -19199,13 +19199,13 @@
         </is>
       </c>
       <c r="N106" t="n">
-        <v>142</v>
+        <v>72</v>
       </c>
       <c r="O106" t="n">
-        <v>142</v>
+        <v>72</v>
       </c>
       <c r="R106" t="n">
-        <v>1.326973020816235</v>
+        <v>1.361707535859717</v>
       </c>
       <c r="S106" t="inlineStr">
         <is>
@@ -19214,7 +19214,7 @@
       </c>
       <c r="U106" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_SALMONELLA</t>
+          <t>SER_NZ_SALMONELLOSIS_MONTHLY</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -19239,7 +19239,7 @@
       </c>
       <c r="AS106" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_SALMONELLA</t>
+          <t>SER_NZ_SALMONELLOSIS_MONTHLY</t>
         </is>
       </c>
       <c r="AT106" t="n">
@@ -19252,42 +19252,42 @@
       </c>
       <c r="AV106" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ106" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="BA106" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB106" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="BC106" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -19319,12 +19319,12 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NZ</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -19358,29 +19358,29 @@
         </is>
       </c>
       <c r="N107" t="n">
-        <v>142</v>
+        <v>72</v>
       </c>
       <c r="O107" t="n">
-        <v>142</v>
+        <v>72</v>
       </c>
       <c r="U107" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_SALMONELLA</t>
+          <t>SER_NZ_SALMONELLOSIS_MONTHLY</t>
         </is>
       </c>
       <c r="V107" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_SALMONELLA</t>
+          <t>SER_NZ_SALMONELLOSIS_MONTHLY</t>
         </is>
       </c>
       <c r="W107" t="inlineStr">
         <is>
-          <t>SRC_SE_FOHM_SMINET</t>
+          <t>SRC_NZ_PHS</t>
         </is>
       </c>
       <c r="X107" t="inlineStr">
         <is>
-          <t>Salmonellainfektion</t>
+          <t>Salmonellosis</t>
         </is>
       </c>
       <c r="Y107" t="inlineStr">
@@ -19390,7 +19390,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -19405,7 +19405,7 @@
       </c>
       <c r="AC107" t="inlineStr">
         <is>
-          <t>country:SE:national</t>
+          <t>country:NZ:national</t>
         </is>
       </c>
       <c r="AD107" t="inlineStr">
@@ -19440,17 +19440,17 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>SE_FOHM_SMINET_current</t>
+          <t>NZ_PHS_current</t>
         </is>
       </c>
       <c r="AK107" t="inlineStr">
         <is>
-          <t>Sweden FHM SmiNet national monthly notification series; Retain FHM source scope alongside separate Typhi and Paratyphi categories.</t>
+          <t>New Zealand PHF Science monthly salmonellosis notifications.</t>
         </is>
       </c>
       <c r="AM107" t="inlineStr">
         <is>
-          <t>revised</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN107" t="b">
@@ -19473,7 +19473,7 @@
       </c>
       <c r="AS107" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_SALMONELLA</t>
+          <t>SER_NZ_SALMONELLOSIS_MONTHLY</t>
         </is>
       </c>
       <c r="AT107" t="n">
@@ -19486,42 +19486,42 @@
       </c>
       <c r="AV107" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ107" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="BA107" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB107" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="BC107" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -19553,12 +19553,12 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -19583,7 +19583,7 @@
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M108" t="inlineStr">
@@ -19592,81 +19592,95 @@
         </is>
       </c>
       <c r="N108" t="n">
-        <v>671</v>
+        <v>142</v>
       </c>
       <c r="O108" t="n">
-        <v>671</v>
+        <v>142</v>
       </c>
       <c r="R108" t="n">
-        <v>0.1922440587088257</v>
+        <v>1.326973020816235</v>
       </c>
       <c r="S108" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U108" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_SALMONELLA</t>
+        </is>
+      </c>
+      <c r="AA108" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO108" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP108" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR108" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS108" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ108" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS108" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_SALMONELLA</t>
+        </is>
+      </c>
       <c r="AT108" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU108" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV108" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ108" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA108" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB108" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC108" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -19693,17 +19707,17 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -19728,7 +19742,7 @@
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M109" t="inlineStr">
@@ -19737,81 +19751,170 @@
         </is>
       </c>
       <c r="N109" t="n">
-        <v>839</v>
+        <v>142</v>
       </c>
       <c r="O109" t="n">
-        <v>839</v>
-      </c>
-      <c r="R109" t="n">
-        <v>0.2403766993393514</v>
-      </c>
-      <c r="S109" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>142</v>
+      </c>
+      <c r="U109" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_SALMONELLA</t>
+        </is>
+      </c>
+      <c r="V109" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_SALMONELLA</t>
+        </is>
+      </c>
+      <c r="W109" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X109" t="inlineStr">
+        <is>
+          <t>Salmonellainfektion</t>
+        </is>
+      </c>
+      <c r="Y109" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z109" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA109" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB109" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC109" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD109" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE109" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF109" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG109" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH109" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI109" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ109" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK109" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; Retain FHM source scope alongside separate Typhi and Paratyphi categories.</t>
+        </is>
+      </c>
+      <c r="AM109" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN109" t="b">
+        <v>1</v>
       </c>
       <c r="AO109" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP109" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR109" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS109" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ109" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS109" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_SALMONELLA</t>
+        </is>
+      </c>
       <c r="AT109" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU109" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV109" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ109" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA109" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB109" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC109" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -19873,7 +19976,7 @@
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="M110" t="inlineStr">
@@ -19882,13 +19985,13 @@
         </is>
       </c>
       <c r="N110" t="n">
-        <v>1110</v>
+        <v>671</v>
       </c>
       <c r="O110" t="n">
-        <v>1110</v>
+        <v>671</v>
       </c>
       <c r="R110" t="n">
-        <v>0.3180192327374018</v>
+        <v>0.1922440587088257</v>
       </c>
       <c r="S110" t="inlineStr">
         <is>
@@ -20018,7 +20121,7 @@
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="M111" t="inlineStr">
@@ -20027,13 +20130,13 @@
         </is>
       </c>
       <c r="N111" t="n">
-        <v>1115</v>
+        <v>839</v>
       </c>
       <c r="O111" t="n">
-        <v>1115</v>
+        <v>839</v>
       </c>
       <c r="R111" t="n">
-        <v>0.3194517518037865</v>
+        <v>0.2403766993393514</v>
       </c>
       <c r="S111" t="inlineStr">
         <is>
@@ -20133,12 +20236,12 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -20163,22 +20266,22 @@
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="M112" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N112" t="n">
-        <v>431</v>
+        <v>1110</v>
       </c>
       <c r="O112" t="n">
-        <v>431</v>
+        <v>1110</v>
       </c>
       <c r="R112" t="n">
-        <v>1.58298189421303</v>
+        <v>0.3180192327374018</v>
       </c>
       <c r="S112" t="inlineStr">
         <is>
@@ -20211,42 +20314,42 @@
       </c>
       <c r="AV112" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ112" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA112" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB112" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC112" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -20278,12 +20381,12 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -20308,104 +20411,90 @@
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="M113" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N113" t="n">
-        <v>27</v>
+        <v>1115</v>
       </c>
       <c r="O113" t="n">
-        <v>27</v>
+        <v>1115</v>
       </c>
       <c r="R113" t="n">
-        <v>0.4802784761333171</v>
+        <v>0.3194517518037865</v>
       </c>
       <c r="S113" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U113" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1200</t>
-        </is>
-      </c>
-      <c r="AA113" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO113" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP113" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ113" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AS113" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1200</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR113" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS113" t="inlineStr"/>
       <c r="AT113" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU113" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV113" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ113" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA113" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB113" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC113" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -20432,17 +20521,17 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -20476,170 +20565,81 @@
         </is>
       </c>
       <c r="N114" t="n">
-        <v>27</v>
+        <v>482</v>
       </c>
       <c r="O114" t="n">
-        <v>27</v>
-      </c>
-      <c r="U114" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1200</t>
-        </is>
-      </c>
-      <c r="V114" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1200</t>
-        </is>
-      </c>
-      <c r="W114" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X114" t="inlineStr">
-        <is>
-          <t>Salmonella, other</t>
-        </is>
-      </c>
-      <c r="Y114" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z114" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA114" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB114" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC114" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD114" t="inlineStr">
+        <v>482</v>
+      </c>
+      <c r="R114" t="n">
+        <v>1.770295297008539</v>
+      </c>
+      <c r="S114" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO114" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP114" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR114" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS114" t="inlineStr"/>
+      <c r="AT114" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU114" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV114" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="AE114" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF114" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG114" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH114" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI114" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ114" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK114" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; Residual Salmonella category excluding Typhi and Paratyphi; retain as its own non-additive series.</t>
-        </is>
-      </c>
-      <c r="AM114" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN114" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO114" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP114" t="inlineStr">
-        <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ114" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AS114" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1200</t>
-        </is>
-      </c>
-      <c r="AT114" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU114" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
-        </is>
-      </c>
-      <c r="AV114" t="inlineStr">
-        <is>
-          <t>thl_ttr</t>
-        </is>
-      </c>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ114" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA114" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB114" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC114" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -20671,12 +20671,12 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -20710,13 +20710,13 @@
         </is>
       </c>
       <c r="N115" t="n">
-        <v>72</v>
+        <v>39</v>
       </c>
       <c r="O115" t="n">
-        <v>72</v>
+        <v>39</v>
       </c>
       <c r="R115" t="n">
-        <v>1.273662594572764</v>
+        <v>0.6937355766370136</v>
       </c>
       <c r="S115" t="inlineStr">
         <is>
@@ -20725,7 +20725,7 @@
       </c>
       <c r="U115" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_302_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1200</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
@@ -20745,12 +20745,12 @@
       </c>
       <c r="AQ115" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AS115" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_302_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1200</t>
         </is>
       </c>
       <c r="AT115" t="n">
@@ -20758,47 +20758,47 @@
       </c>
       <c r="AU115" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV115" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ115" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA115" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB115" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC115" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -20830,12 +20830,12 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -20869,29 +20869,29 @@
         </is>
       </c>
       <c r="N116" t="n">
-        <v>72</v>
+        <v>39</v>
       </c>
       <c r="O116" t="n">
-        <v>72</v>
+        <v>39</v>
       </c>
       <c r="U116" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_302_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1200</t>
         </is>
       </c>
       <c r="V116" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_302_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1200</t>
         </is>
       </c>
       <c r="W116" t="inlineStr">
         <is>
-          <t>SRC_NO_FHI_MSIS</t>
+          <t>SRC_FI_THL_TTR</t>
         </is>
       </c>
       <c r="X116" t="inlineStr">
         <is>
-          <t>Salmonellose</t>
+          <t>Salmonella, other</t>
         </is>
       </c>
       <c r="Y116" t="inlineStr">
@@ -20916,7 +20916,7 @@
       </c>
       <c r="AC116" t="inlineStr">
         <is>
-          <t>country:NO:national</t>
+          <t>country:FI:national</t>
         </is>
       </c>
       <c r="AD116" t="inlineStr">
@@ -20951,17 +20951,17 @@
       </c>
       <c r="AJ116" t="inlineStr">
         <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+          <t>FI_THL_TTR_reporting_group</t>
         </is>
       </c>
       <c r="AK116" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+          <t>Finland THL national monthly notification series; Residual Salmonella category excluding Typhi and Paratyphi; retain as its own non-additive series.</t>
         </is>
       </c>
       <c r="AM116" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN116" t="b">
@@ -20979,12 +20979,12 @@
       </c>
       <c r="AQ116" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AS116" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_302_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1200</t>
         </is>
       </c>
       <c r="AT116" t="n">
@@ -20992,47 +20992,47 @@
       </c>
       <c r="AU116" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV116" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ116" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA116" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB116" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC116" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -21064,12 +21064,12 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -21103,81 +21103,95 @@
         </is>
       </c>
       <c r="N117" t="n">
-        <v>1166</v>
+        <v>94</v>
       </c>
       <c r="O117" t="n">
-        <v>1166</v>
+        <v>94</v>
       </c>
       <c r="R117" t="n">
-        <v>0.3340634462809103</v>
+        <v>1.662837276247776</v>
       </c>
       <c r="S117" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U117" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_302_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA117" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO117" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP117" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR117" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS117" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ117" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS117" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_302_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT117" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU117" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV117" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ117" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA117" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB117" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC117" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -21204,17 +21218,17 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -21239,7 +21253,7 @@
       </c>
       <c r="L118" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M118" t="inlineStr">
@@ -21248,81 +21262,170 @@
         </is>
       </c>
       <c r="N118" t="n">
-        <v>1060</v>
+        <v>94</v>
       </c>
       <c r="O118" t="n">
-        <v>1060</v>
-      </c>
-      <c r="R118" t="n">
-        <v>0.3036940420735548</v>
-      </c>
-      <c r="S118" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>94</v>
+      </c>
+      <c r="U118" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_302_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V118" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_302_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W118" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X118" t="inlineStr">
+        <is>
+          <t>Salmonellose</t>
+        </is>
+      </c>
+      <c r="Y118" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z118" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA118" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB118" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC118" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD118" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE118" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF118" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG118" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH118" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI118" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ118" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK118" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM118" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN118" t="b">
+        <v>1</v>
       </c>
       <c r="AO118" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP118" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR118" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS118" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ118" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS118" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_302_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT118" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU118" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV118" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ118" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA118" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB118" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC118" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -21384,7 +21487,7 @@
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M119" t="inlineStr">
@@ -21393,13 +21496,13 @@
         </is>
       </c>
       <c r="N119" t="n">
-        <v>1056</v>
+        <v>1166</v>
       </c>
       <c r="O119" t="n">
-        <v>1056</v>
+        <v>1166</v>
       </c>
       <c r="R119" t="n">
-        <v>0.3025480268204471</v>
+        <v>0.3340634462809103</v>
       </c>
       <c r="S119" t="inlineStr">
         <is>
@@ -21466,6 +21569,296 @@
         </is>
       </c>
       <c r="BC119" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>D114</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>salmonellosis</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>Salmonellosis</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>D114</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>Salmonellosis</t>
+        </is>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>沙门氏菌病</t>
+        </is>
+      </c>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L120" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N120" t="n">
+        <v>1060</v>
+      </c>
+      <c r="O120" t="n">
+        <v>1060</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0.3036940420735548</v>
+      </c>
+      <c r="S120" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO120" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP120" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR120" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS120" t="inlineStr"/>
+      <c r="AT120" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU120" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV120" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW120" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX120" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY120" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ120" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA120" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB120" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC120" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>D114</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>salmonellosis</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>Salmonellosis</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>D114</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>Salmonellosis</t>
+        </is>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>沙门氏菌病</t>
+        </is>
+      </c>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L121" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="M121" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N121" t="n">
+        <v>1056</v>
+      </c>
+      <c r="O121" t="n">
+        <v>1056</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0.3025480268204471</v>
+      </c>
+      <c r="S121" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO121" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP121" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR121" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS121" t="inlineStr"/>
+      <c r="AT121" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU121" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV121" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW121" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX121" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY121" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ121" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA121" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB121" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC121" t="inlineStr">
         <is>
           <t>api; api</t>
         </is>
@@ -21587,7 +21980,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="10">
@@ -21597,7 +21990,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>118</v>
+        <v>120</v>
       </c>
     </row>
     <row r="11">
@@ -21617,7 +22010,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="13">
@@ -21649,7 +22042,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>29864</v>
+        <v>30022</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d114/2026-2029.xlsx
+++ b/diseases/d114/2026-2029.xlsx
@@ -18123,13 +18123,13 @@
         </is>
       </c>
       <c r="N100" t="n">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="O100" t="n">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="R100" t="n">
-        <v>2.651770133693288</v>
+        <v>2.655442945512808</v>
       </c>
       <c r="S100" t="inlineStr">
         <is>
@@ -20565,13 +20565,13 @@
         </is>
       </c>
       <c r="N114" t="n">
-        <v>482</v>
+        <v>509</v>
       </c>
       <c r="O114" t="n">
-        <v>482</v>
+        <v>509</v>
       </c>
       <c r="R114" t="n">
-        <v>1.770295297008539</v>
+        <v>1.869461216135573</v>
       </c>
       <c r="S114" t="inlineStr">
         <is>
@@ -22042,7 +22042,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>30022</v>
+        <v>30050</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d114/2026-2029.xlsx
+++ b/diseases/d114/2026-2029.xlsx
@@ -32385,13 +32385,13 @@
         </is>
       </c>
       <c r="N174" t="n">
-        <v>509</v>
+        <v>524</v>
       </c>
       <c r="O174" t="n">
-        <v>509</v>
+        <v>524</v>
       </c>
       <c r="R174" t="n">
-        <v>1.869461216135573</v>
+        <v>1.92455339342837</v>
       </c>
       <c r="S174" t="inlineStr">
         <is>
@@ -35189,7 +35189,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>31877</v>
+        <v>31892</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d114/2026-2029.xlsx
+++ b/diseases/d114/2026-2029.xlsx
@@ -1473,7 +1473,7 @@
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
@@ -1481,17 +1481,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR6" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS6" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1200</t>
         </is>
       </c>
       <c r="AT6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
@@ -1707,7 +1712,7 @@
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
@@ -1715,17 +1720,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR7" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS7" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1200</t>
         </is>
       </c>
       <c r="AT7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
@@ -1866,7 +1876,7 @@
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
@@ -1874,17 +1884,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR8" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS8" t="inlineStr">
         <is>
           <t>SER_NO_FHI_302_MONTHLY</t>
         </is>
       </c>
       <c r="AT8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV8" t="inlineStr">
@@ -2100,7 +2115,7 @@
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
@@ -2108,17 +2123,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR9" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS9" t="inlineStr">
         <is>
           <t>SER_NO_FHI_302_MONTHLY</t>
         </is>
       </c>
       <c r="AT9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV9" t="inlineStr">
@@ -2655,7 +2675,7 @@
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
@@ -2663,17 +2683,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR12" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS12" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_SALMONELLA</t>
         </is>
       </c>
       <c r="AT12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV12" t="inlineStr">
@@ -2889,7 +2914,7 @@
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
@@ -2897,17 +2922,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR13" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS13" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_SALMONELLA</t>
         </is>
       </c>
       <c r="AT13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV13" t="inlineStr">
@@ -6047,7 +6077,7 @@
       </c>
       <c r="AP31" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ31" t="inlineStr">
@@ -6055,17 +6085,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR31" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS31" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1200</t>
         </is>
       </c>
       <c r="AT31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU31" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV31" t="inlineStr">
@@ -6281,7 +6316,7 @@
       </c>
       <c r="AP32" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ32" t="inlineStr">
@@ -6289,17 +6324,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR32" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS32" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1200</t>
         </is>
       </c>
       <c r="AT32" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU32" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV32" t="inlineStr">
@@ -6440,7 +6480,7 @@
       </c>
       <c r="AP33" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ33" t="inlineStr">
@@ -6448,17 +6488,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR33" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS33" t="inlineStr">
         <is>
           <t>SER_NO_FHI_302_MONTHLY</t>
         </is>
       </c>
       <c r="AT33" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU33" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV33" t="inlineStr">
@@ -6674,7 +6719,7 @@
       </c>
       <c r="AP34" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ34" t="inlineStr">
@@ -6682,17 +6727,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR34" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS34" t="inlineStr">
         <is>
           <t>SER_NO_FHI_302_MONTHLY</t>
         </is>
       </c>
       <c r="AT34" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU34" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV34" t="inlineStr">
@@ -7229,7 +7279,7 @@
       </c>
       <c r="AP37" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ37" t="inlineStr">
@@ -7237,17 +7287,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR37" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS37" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_SALMONELLA</t>
         </is>
       </c>
       <c r="AT37" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU37" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV37" t="inlineStr">
@@ -7463,7 +7518,7 @@
       </c>
       <c r="AP38" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ38" t="inlineStr">
@@ -7471,17 +7526,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR38" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS38" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_SALMONELLA</t>
         </is>
       </c>
       <c r="AT38" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU38" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV38" t="inlineStr">
@@ -10473,7 +10533,7 @@
       </c>
       <c r="AP55" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ55" t="inlineStr">
@@ -10481,17 +10541,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR55" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS55" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1200</t>
         </is>
       </c>
       <c r="AT55" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU55" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV55" t="inlineStr">
@@ -10707,7 +10772,7 @@
       </c>
       <c r="AP56" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ56" t="inlineStr">
@@ -10715,17 +10780,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR56" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS56" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1200</t>
         </is>
       </c>
       <c r="AT56" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU56" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV56" t="inlineStr">
@@ -10866,7 +10936,7 @@
       </c>
       <c r="AP57" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ57" t="inlineStr">
@@ -10874,17 +10944,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR57" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS57" t="inlineStr">
         <is>
           <t>SER_NO_FHI_302_MONTHLY</t>
         </is>
       </c>
       <c r="AT57" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU57" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV57" t="inlineStr">
@@ -11100,7 +11175,7 @@
       </c>
       <c r="AP58" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ58" t="inlineStr">
@@ -11108,17 +11183,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR58" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS58" t="inlineStr">
         <is>
           <t>SER_NO_FHI_302_MONTHLY</t>
         </is>
       </c>
       <c r="AT58" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU58" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV58" t="inlineStr">
@@ -11655,7 +11735,7 @@
       </c>
       <c r="AP61" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ61" t="inlineStr">
@@ -11663,17 +11743,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR61" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS61" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_SALMONELLA</t>
         </is>
       </c>
       <c r="AT61" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU61" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV61" t="inlineStr">
@@ -11889,7 +11974,7 @@
       </c>
       <c r="AP62" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ62" t="inlineStr">
@@ -11897,17 +11982,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR62" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS62" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_SALMONELLA</t>
         </is>
       </c>
       <c r="AT62" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU62" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV62" t="inlineStr">
@@ -15290,7 +15380,7 @@
       </c>
       <c r="AP81" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ81" t="inlineStr">
@@ -15298,17 +15388,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR81" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS81" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1200</t>
         </is>
       </c>
       <c r="AT81" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU81" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV81" t="inlineStr">
@@ -15524,7 +15619,7 @@
       </c>
       <c r="AP82" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ82" t="inlineStr">
@@ -15532,17 +15627,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR82" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS82" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1200</t>
         </is>
       </c>
       <c r="AT82" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU82" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV82" t="inlineStr">
@@ -15683,7 +15783,7 @@
       </c>
       <c r="AP83" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ83" t="inlineStr">
@@ -15691,17 +15791,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR83" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS83" t="inlineStr">
         <is>
           <t>SER_NO_FHI_302_MONTHLY</t>
         </is>
       </c>
       <c r="AT83" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU83" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV83" t="inlineStr">
@@ -15917,7 +16022,7 @@
       </c>
       <c r="AP84" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ84" t="inlineStr">
@@ -15925,17 +16030,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR84" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS84" t="inlineStr">
         <is>
           <t>SER_NO_FHI_302_MONTHLY</t>
         </is>
       </c>
       <c r="AT84" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU84" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV84" t="inlineStr">
@@ -16469,7 +16579,7 @@
       </c>
       <c r="AP87" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ87" t="inlineStr">
@@ -16477,17 +16587,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR87" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS87" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_SALMONELLA</t>
         </is>
       </c>
       <c r="AT87" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU87" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV87" t="inlineStr">
@@ -16703,7 +16818,7 @@
       </c>
       <c r="AP88" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ88" t="inlineStr">
@@ -16711,17 +16826,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR88" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS88" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_SALMONELLA</t>
         </is>
       </c>
       <c r="AT88" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU88" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV88" t="inlineStr">
@@ -19710,7 +19830,7 @@
       </c>
       <c r="AP105" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ105" t="inlineStr">
@@ -19718,17 +19838,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR105" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS105" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1200</t>
         </is>
       </c>
       <c r="AT105" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU105" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV105" t="inlineStr">
@@ -19944,7 +20069,7 @@
       </c>
       <c r="AP106" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ106" t="inlineStr">
@@ -19952,17 +20077,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR106" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS106" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1200</t>
         </is>
       </c>
       <c r="AT106" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU106" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV106" t="inlineStr">
@@ -20103,7 +20233,7 @@
       </c>
       <c r="AP107" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ107" t="inlineStr">
@@ -20111,17 +20241,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR107" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS107" t="inlineStr">
         <is>
           <t>SER_NO_FHI_302_MONTHLY</t>
         </is>
       </c>
       <c r="AT107" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU107" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV107" t="inlineStr">
@@ -20337,7 +20472,7 @@
       </c>
       <c r="AP108" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ108" t="inlineStr">
@@ -20345,17 +20480,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR108" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS108" t="inlineStr">
         <is>
           <t>SER_NO_FHI_302_MONTHLY</t>
         </is>
       </c>
       <c r="AT108" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU108" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV108" t="inlineStr">
@@ -20889,7 +21029,7 @@
       </c>
       <c r="AP111" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ111" t="inlineStr">
@@ -20897,17 +21037,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR111" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS111" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_SALMONELLA</t>
         </is>
       </c>
       <c r="AT111" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU111" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV111" t="inlineStr">
@@ -21123,7 +21268,7 @@
       </c>
       <c r="AP112" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ112" t="inlineStr">
@@ -21131,17 +21276,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR112" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS112" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_SALMONELLA</t>
         </is>
       </c>
       <c r="AT112" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU112" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV112" t="inlineStr">
@@ -24669,7 +24819,7 @@
       </c>
       <c r="AP132" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ132" t="inlineStr">
@@ -24677,17 +24827,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR132" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS132" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1200</t>
         </is>
       </c>
       <c r="AT132" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU132" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV132" t="inlineStr">
@@ -24903,7 +25058,7 @@
       </c>
       <c r="AP133" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ133" t="inlineStr">
@@ -24911,17 +25066,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR133" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS133" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1200</t>
         </is>
       </c>
       <c r="AT133" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU133" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV133" t="inlineStr">
@@ -25062,7 +25222,7 @@
       </c>
       <c r="AP134" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ134" t="inlineStr">
@@ -25070,17 +25230,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR134" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS134" t="inlineStr">
         <is>
           <t>SER_NO_FHI_302_MONTHLY</t>
         </is>
       </c>
       <c r="AT134" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU134" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV134" t="inlineStr">
@@ -25296,7 +25461,7 @@
       </c>
       <c r="AP135" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ135" t="inlineStr">
@@ -25304,17 +25469,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR135" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS135" t="inlineStr">
         <is>
           <t>SER_NO_FHI_302_MONTHLY</t>
         </is>
       </c>
       <c r="AT135" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU135" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV135" t="inlineStr">
@@ -25848,7 +26018,7 @@
       </c>
       <c r="AP138" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ138" t="inlineStr">
@@ -25856,17 +26026,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR138" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS138" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_SALMONELLA</t>
         </is>
       </c>
       <c r="AT138" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU138" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV138" t="inlineStr">
@@ -26082,7 +26257,7 @@
       </c>
       <c r="AP139" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ139" t="inlineStr">
@@ -26090,17 +26265,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR139" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS139" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_SALMONELLA</t>
         </is>
       </c>
       <c r="AT139" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU139" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV139" t="inlineStr">
@@ -28687,7 +28867,7 @@
       </c>
       <c r="AP154" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ154" t="inlineStr">
@@ -28695,17 +28875,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR154" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS154" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1200</t>
         </is>
       </c>
       <c r="AT154" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU154" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV154" t="inlineStr">
@@ -28921,7 +29106,7 @@
       </c>
       <c r="AP155" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ155" t="inlineStr">
@@ -28929,17 +29114,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR155" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS155" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1200</t>
         </is>
       </c>
       <c r="AT155" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU155" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV155" t="inlineStr">
@@ -29080,7 +29270,7 @@
       </c>
       <c r="AP156" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ156" t="inlineStr">
@@ -29088,17 +29278,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR156" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS156" t="inlineStr">
         <is>
           <t>SER_NO_FHI_302_MONTHLY</t>
         </is>
       </c>
       <c r="AT156" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU156" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV156" t="inlineStr">
@@ -29314,7 +29509,7 @@
       </c>
       <c r="AP157" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ157" t="inlineStr">
@@ -29322,17 +29517,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR157" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS157" t="inlineStr">
         <is>
           <t>SER_NO_FHI_302_MONTHLY</t>
         </is>
       </c>
       <c r="AT157" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU157" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV157" t="inlineStr">
@@ -29866,7 +30066,7 @@
       </c>
       <c r="AP160" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ160" t="inlineStr">
@@ -29874,17 +30074,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR160" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS160" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_SALMONELLA</t>
         </is>
       </c>
       <c r="AT160" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU160" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV160" t="inlineStr">
@@ -30100,7 +30305,7 @@
       </c>
       <c r="AP161" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ161" t="inlineStr">
@@ -30108,17 +30313,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR161" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS161" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_SALMONELLA</t>
         </is>
       </c>
       <c r="AT161" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU161" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV161" t="inlineStr">
@@ -32385,13 +32595,13 @@
         </is>
       </c>
       <c r="N174" t="n">
-        <v>524</v>
+        <v>535</v>
       </c>
       <c r="O174" t="n">
-        <v>524</v>
+        <v>535</v>
       </c>
       <c r="R174" t="n">
-        <v>1.92455339342837</v>
+        <v>1.964954323443088</v>
       </c>
       <c r="S174" t="inlineStr">
         <is>
@@ -32560,7 +32770,7 @@
       </c>
       <c r="AP175" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ175" t="inlineStr">
@@ -32568,17 +32778,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR175" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS175" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1200</t>
         </is>
       </c>
       <c r="AT175" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU175" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV175" t="inlineStr">
@@ -32794,7 +33009,7 @@
       </c>
       <c r="AP176" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ176" t="inlineStr">
@@ -32802,17 +33017,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR176" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS176" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1200</t>
         </is>
       </c>
       <c r="AT176" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU176" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV176" t="inlineStr">
@@ -32953,7 +33173,7 @@
       </c>
       <c r="AP177" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ177" t="inlineStr">
@@ -32961,17 +33181,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR177" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS177" t="inlineStr">
         <is>
           <t>SER_NO_FHI_302_MONTHLY</t>
         </is>
       </c>
       <c r="AT177" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU177" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV177" t="inlineStr">
@@ -33187,7 +33412,7 @@
       </c>
       <c r="AP178" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ178" t="inlineStr">
@@ -33195,17 +33420,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR178" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS178" t="inlineStr">
         <is>
           <t>SER_NO_FHI_302_MONTHLY</t>
         </is>
       </c>
       <c r="AT178" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU178" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV178" t="inlineStr">
@@ -35189,7 +35419,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>31892</v>
+        <v>31903</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d114/2026-2029.xlsx
+++ b/diseases/d114/2026-2029.xlsx
@@ -34867,13 +34867,13 @@
         </is>
       </c>
       <c r="N190" t="n">
-        <v>625</v>
+        <v>632</v>
       </c>
       <c r="O190" t="n">
-        <v>625</v>
+        <v>632</v>
       </c>
       <c r="R190" t="n">
-        <v>2.295507387199869</v>
+        <v>2.321217069936508</v>
       </c>
       <c r="S190" t="inlineStr">
         <is>
@@ -39255,13 +39255,13 @@
         </is>
       </c>
       <c r="N216" t="n">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="O216" t="n">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="R216" t="n">
-        <v>0.02938249455615832</v>
+        <v>0.09549310730751455</v>
       </c>
       <c r="S216" t="inlineStr">
         <is>
@@ -40317,7 +40317,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>35153</v>
+        <v>35178</v>
       </c>
     </row>
     <row r="16">
